--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="17329"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Trans\STAFF\Reid\viz\rhaefer.github.io\ski tours\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11685"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="177">
   <si>
     <t>id</t>
   </si>
@@ -541,55 +533,51 @@
   </si>
   <si>
     <t>https://goo.gl/photos/yNGMB948gbX3odZN8</t>
+  </si>
+  <si>
+    <t>We toured up to Camp Muir one of the first sunny spring days of 2017. We booted up Panorama Point and skinned all the way to Muir without the need for crampons.The ski down was miserable above 9000 feet and pretty fun below. We skiied all the way back to the Paradise Parking lot.</t>
+  </si>
+  <si>
+    <t>Even though it was a sunny, warm day the skiing above 9 thousand feet was terrible; it was hard, wind scoured, and sun cupped. I've done camp muir several times and this always seems to be the case. In terms of experiencing fun skiing, there doesn't seem to be any reason to go all the way to muir. The good skiing seems to always start around 8500.</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/vbwSH4zZGAcjfWYZ7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
+  </numFmts>
   <fonts count="8">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+    </font>
+    <font/>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
-      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF2A2A2A"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arimo"/>
     </font>
@@ -599,7 +587,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -620,366 +608,87 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+  <cellXfs count="14">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X22"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="32.140625" customWidth="1"/>
-    <col min="11" max="11" width="34.42578125" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" customWidth="1"/>
-    <col min="13" max="13" width="24.42578125" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" customWidth="1"/>
-    <col min="17" max="18" width="19.140625" customWidth="1"/>
-    <col min="19" max="19" width="21.42578125" customWidth="1"/>
-    <col min="20" max="20" width="18.7109375" customWidth="1"/>
-    <col min="22" max="22" width="34.5703125" customWidth="1"/>
-    <col min="23" max="23" width="21.42578125" customWidth="1"/>
-    <col min="24" max="24" width="42" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="11.0"/>
+    <col customWidth="1" min="3" max="3" width="18.86"/>
+    <col customWidth="1" min="4" max="4" width="24.71"/>
+    <col customWidth="1" min="5" max="5" width="17.86"/>
+    <col customWidth="1" min="6" max="6" width="17.71"/>
+    <col customWidth="1" min="7" max="7" width="26.71"/>
+    <col customWidth="1" min="8" max="8" width="46.0"/>
+    <col customWidth="1" min="9" max="9" width="20.86"/>
+    <col customWidth="1" min="10" max="10" width="32.14"/>
+    <col customWidth="1" min="11" max="11" width="34.43"/>
+    <col customWidth="1" min="12" max="12" width="16.71"/>
+    <col customWidth="1" min="13" max="13" width="24.43"/>
+    <col customWidth="1" min="14" max="14" width="6.86"/>
+    <col customWidth="1" min="15" max="15" width="6.43"/>
+    <col customWidth="1" min="17" max="18" width="19.14"/>
+    <col customWidth="1" min="19" max="19" width="21.43"/>
+    <col customWidth="1" min="20" max="20" width="18.71"/>
+    <col customWidth="1" min="22" max="22" width="34.57"/>
+    <col customWidth="1" min="23" max="23" width="21.43"/>
+    <col customWidth="1" min="24" max="24" width="42.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,12 +762,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="15.75" customHeight="1">
+    <row r="2">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B2" s="4">
-        <v>42721</v>
+        <v>42721.0</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>24</v>
@@ -1079,7 +788,7 @@
         <v>29</v>
       </c>
       <c r="I2" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>30</v>
@@ -1094,29 +803,29 @@
         <v>33</v>
       </c>
       <c r="N2" s="3">
-        <v>850</v>
+        <v>850.0</v>
       </c>
       <c r="O2" s="3">
-        <v>1550</v>
-      </c>
-      <c r="P2" t="e">
-        <f t="shared" ref="P2:P19" ca="1" si="0">_xludf.CONCAT((O2-N2)/100," hours")</f>
-        <v>#NAME?</v>
+        <v>1550.0</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2:P19" si="1">CONCAT((O2-N2)/100," hours")</f>
+        <v>7 hours</v>
       </c>
       <c r="Q2" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="S2" s="3">
-        <v>3600</v>
+        <v>3600.0</v>
       </c>
       <c r="T2" s="3">
-        <v>1000</v>
+        <v>1000.0</v>
       </c>
       <c r="U2" s="3">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="V2" s="3" t="s">
         <v>35</v>
@@ -1128,12 +837,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1">
+    <row r="3">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B3" s="4">
-        <v>42722</v>
+        <v>42722.0</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1154,7 +863,7 @@
         <v>29</v>
       </c>
       <c r="I3" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>39</v>
@@ -1169,29 +878,29 @@
         <v>33</v>
       </c>
       <c r="N3" s="3">
-        <v>850</v>
+        <v>850.0</v>
       </c>
       <c r="O3" s="3">
-        <v>1550</v>
-      </c>
-      <c r="P3" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1550.0</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" si="1"/>
+        <v>7 hours</v>
       </c>
       <c r="Q3" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>34</v>
       </c>
       <c r="S3" s="3">
-        <v>3600</v>
+        <v>3600.0</v>
       </c>
       <c r="T3" s="3">
-        <v>1000</v>
+        <v>1000.0</v>
       </c>
       <c r="U3" s="3">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>40</v>
@@ -1203,12 +912,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1">
+    <row r="4">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B4" s="4">
-        <v>42714</v>
+        <v>42714.0</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>42</v>
@@ -1229,7 +938,7 @@
         <v>45</v>
       </c>
       <c r="I4" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>46</v>
@@ -1244,29 +953,29 @@
         <v>48</v>
       </c>
       <c r="N4" s="3">
-        <v>1050</v>
+        <v>1050.0</v>
       </c>
       <c r="O4" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P4" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1700.0</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="1"/>
+        <v>6.5 hours</v>
       </c>
       <c r="Q4" s="3">
-        <v>3600</v>
+        <v>3600.0</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="S4" s="3">
-        <v>5200</v>
+        <v>5200.0</v>
       </c>
       <c r="T4" s="3">
-        <v>2000</v>
+        <v>2000.0</v>
       </c>
       <c r="U4" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>50</v>
@@ -1278,12 +987,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1">
+    <row r="5">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="B5" s="4">
-        <v>42707</v>
+        <v>42707.0</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>52</v>
@@ -1304,7 +1013,7 @@
         <v>54</v>
       </c>
       <c r="I5" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>55</v>
@@ -1319,29 +1028,29 @@
         <v>56</v>
       </c>
       <c r="N5" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O5" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P5" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1400.0</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="1"/>
+        <v>4.5 hours</v>
       </c>
       <c r="Q5" s="3">
-        <v>4400</v>
+        <v>4400.0</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>57</v>
       </c>
       <c r="S5" s="3">
-        <v>6400</v>
+        <v>6400.0</v>
       </c>
       <c r="T5" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="U5" s="3">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>58</v>
@@ -1353,12 +1062,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="15.75" customHeight="1">
+    <row r="6">
       <c r="A6" s="3">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B6" s="4">
-        <v>42701</v>
+        <v>42701.0</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>42</v>
@@ -1379,7 +1088,7 @@
         <v>61</v>
       </c>
       <c r="I6" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>62</v>
@@ -1394,29 +1103,29 @@
         <v>63</v>
       </c>
       <c r="N6" s="3">
-        <v>1000</v>
+        <v>1000.0</v>
       </c>
       <c r="O6" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P6" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1600.0</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="1"/>
+        <v>6 hours</v>
       </c>
       <c r="Q6" s="3">
-        <v>4000</v>
+        <v>4000.0</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>64</v>
       </c>
       <c r="S6" s="3">
-        <v>5600</v>
+        <v>5600.0</v>
       </c>
       <c r="T6" s="3">
-        <v>2000</v>
+        <v>2000.0</v>
       </c>
       <c r="U6" s="3">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>65</v>
@@ -1428,12 +1137,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1">
+    <row r="7">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="B7" s="4">
-        <v>42693</v>
+        <v>42693.0</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>66</v>
@@ -1454,7 +1163,7 @@
         <v>68</v>
       </c>
       <c r="I7" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>69</v>
@@ -1469,29 +1178,29 @@
         <v>70</v>
       </c>
       <c r="N7" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O7" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P7" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1600.0</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="1"/>
+        <v>6.5 hours</v>
       </c>
       <c r="Q7" s="3">
-        <v>5400</v>
+        <v>5400.0</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>49</v>
       </c>
       <c r="S7" s="3">
-        <v>6300</v>
+        <v>6300.0</v>
       </c>
       <c r="T7" s="3">
-        <v>3000</v>
+        <v>3000.0</v>
       </c>
       <c r="U7" s="3">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>71</v>
@@ -1503,12 +1212,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1">
+    <row r="8">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="B8" s="4">
-        <v>42665</v>
+        <v>42665.0</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>73</v>
@@ -1529,7 +1238,7 @@
         <v>75</v>
       </c>
       <c r="I8" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>76</v>
@@ -1544,14 +1253,14 @@
         <v>77</v>
       </c>
       <c r="N8" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O8" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P8" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1600.0</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="1"/>
+        <v>6.5 hours</v>
       </c>
       <c r="Q8" s="3">
         <f>S8-T8</f>
@@ -1561,13 +1270,13 @@
         <v>49</v>
       </c>
       <c r="S8" s="8">
-        <v>10080</v>
+        <v>10080.0</v>
       </c>
       <c r="T8" s="3">
-        <v>4680</v>
+        <v>4680.0</v>
       </c>
       <c r="U8" s="3">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>78</v>
@@ -1579,12 +1288,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1">
+    <row r="9">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="B9" s="4">
-        <v>42749</v>
+        <v>42749.0</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>24</v>
@@ -1605,7 +1314,7 @@
         <v>54</v>
       </c>
       <c r="I9" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>80</v>
@@ -1620,29 +1329,29 @@
         <v>82</v>
       </c>
       <c r="N9" s="3">
-        <v>675</v>
+        <v>675.0</v>
       </c>
       <c r="O9" s="3">
-        <v>1250</v>
-      </c>
-      <c r="P9" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1250.0</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="1"/>
+        <v>5.75 hours</v>
       </c>
       <c r="Q9" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>83</v>
       </c>
       <c r="S9" s="3">
-        <v>5800</v>
+        <v>5800.0</v>
       </c>
       <c r="T9" s="3">
-        <v>3200</v>
+        <v>3200.0</v>
       </c>
       <c r="U9" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>84</v>
@@ -1654,12 +1363,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1">
+    <row r="10">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="B10" s="4">
-        <v>42750</v>
+        <v>42750.0</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>24</v>
@@ -1680,7 +1389,7 @@
         <v>86</v>
       </c>
       <c r="I10" s="3">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>87</v>
@@ -1695,29 +1404,29 @@
         <v>88</v>
       </c>
       <c r="N10" s="3">
-        <v>700</v>
+        <v>700.0</v>
       </c>
       <c r="O10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P10" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1500.0</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="1"/>
+        <v>8 hours</v>
       </c>
       <c r="Q10" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>89</v>
       </c>
       <c r="S10" s="3">
-        <v>5800</v>
+        <v>5800.0</v>
       </c>
       <c r="T10" s="3">
-        <v>5000</v>
+        <v>5000.0</v>
       </c>
       <c r="U10" s="3">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>90</v>
@@ -1729,12 +1438,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1">
+    <row r="11">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="B11" s="4">
-        <v>42756</v>
+        <v>42756.0</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>92</v>
@@ -1755,7 +1464,7 @@
         <v>94</v>
       </c>
       <c r="I11" s="3">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>95</v>
@@ -1770,17 +1479,17 @@
         <v>97</v>
       </c>
       <c r="N11" s="3">
-        <v>1050</v>
+        <v>1050.0</v>
       </c>
       <c r="O11" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P11" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1800.0</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="1"/>
+        <v>7.5 hours</v>
       </c>
       <c r="Q11" s="3">
-        <v>3800</v>
+        <v>3800.0</v>
       </c>
       <c r="R11" s="5" t="s">
         <v>98</v>
@@ -1790,10 +1499,10 @@
         <v>6300</v>
       </c>
       <c r="T11" s="3">
-        <v>2500</v>
+        <v>2500.0</v>
       </c>
       <c r="U11" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>99</v>
@@ -1805,12 +1514,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1">
+    <row r="12">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="B12" s="4">
-        <v>42764</v>
+        <v>42764.0</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>24</v>
@@ -1831,7 +1540,7 @@
         <v>103</v>
       </c>
       <c r="I12" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>104</v>
@@ -1846,29 +1555,29 @@
         <v>106</v>
       </c>
       <c r="N12" s="3">
-        <v>800</v>
+        <v>800.0</v>
       </c>
       <c r="O12" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P12" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1700.0</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="1"/>
+        <v>9 hours</v>
       </c>
       <c r="Q12" s="3">
-        <v>3000</v>
+        <v>3000.0</v>
       </c>
       <c r="R12" s="5" t="s">
         <v>107</v>
       </c>
       <c r="S12" s="3">
-        <v>5400</v>
+        <v>5400.0</v>
       </c>
       <c r="T12" s="3">
-        <v>3500</v>
+        <v>3500.0</v>
       </c>
       <c r="U12" s="3">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>108</v>
@@ -1880,12 +1589,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1">
+    <row r="13">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="B13" s="4">
-        <v>42772</v>
+        <v>42772.0</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>24</v>
@@ -1906,7 +1615,7 @@
         <v>112</v>
       </c>
       <c r="I13" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>113</v>
@@ -1921,29 +1630,29 @@
         <v>115</v>
       </c>
       <c r="N13" s="3">
-        <v>1500</v>
+        <v>1500.0</v>
       </c>
       <c r="O13" s="3">
-        <v>1750</v>
-      </c>
-      <c r="P13" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1750.0</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="1"/>
+        <v>2.5 hours</v>
       </c>
       <c r="Q13" s="3">
-        <v>3000</v>
+        <v>3000.0</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>116</v>
       </c>
       <c r="S13" s="3">
-        <v>4000</v>
+        <v>4000.0</v>
       </c>
       <c r="T13" s="3">
-        <v>2000</v>
+        <v>2000.0</v>
       </c>
       <c r="U13" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>117</v>
@@ -1955,12 +1664,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1">
+    <row r="14">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="B14" s="4">
-        <v>42778</v>
+        <v>42778.0</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>24</v>
@@ -1981,7 +1690,7 @@
         <v>119</v>
       </c>
       <c r="I14" s="3">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>120</v>
@@ -1996,29 +1705,29 @@
         <v>121</v>
       </c>
       <c r="N14" s="3">
-        <v>850</v>
+        <v>850.0</v>
       </c>
       <c r="O14" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P14" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1400.0</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="1"/>
+        <v>5.5 hours</v>
       </c>
       <c r="Q14" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>122</v>
       </c>
       <c r="S14" s="3">
-        <v>5800</v>
+        <v>5800.0</v>
       </c>
       <c r="T14" s="3">
-        <v>3200</v>
+        <v>3200.0</v>
       </c>
       <c r="U14" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>84</v>
@@ -2030,12 +1739,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1">
+    <row r="15">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="B15" s="4">
-        <v>42784</v>
+        <v>42784.0</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>124</v>
@@ -2056,7 +1765,7 @@
         <v>112</v>
       </c>
       <c r="I15" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>126</v>
@@ -2071,29 +1780,29 @@
         <v>127</v>
       </c>
       <c r="N15" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O15" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P15" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1600.0</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="1"/>
+        <v>6.5 hours</v>
       </c>
       <c r="Q15" s="3">
-        <v>4600</v>
+        <v>4600.0</v>
       </c>
       <c r="R15" s="5" t="s">
         <v>49</v>
       </c>
       <c r="S15" s="3">
-        <v>7000</v>
+        <v>7000.0</v>
       </c>
       <c r="T15" s="3">
-        <v>3000</v>
+        <v>3000.0</v>
       </c>
       <c r="U15" s="3">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>128</v>
@@ -2105,12 +1814,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1">
+    <row r="16">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="B16" s="4">
-        <v>42785</v>
+        <v>42785.0</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>124</v>
@@ -2131,7 +1840,7 @@
         <v>112</v>
       </c>
       <c r="I16" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>131</v>
@@ -2146,29 +1855,29 @@
         <v>132</v>
       </c>
       <c r="N16" s="3">
-        <v>900</v>
+        <v>900.0</v>
       </c>
       <c r="O16" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P16" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1700.0</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="1"/>
+        <v>8 hours</v>
       </c>
       <c r="Q16" s="3">
-        <v>4190</v>
+        <v>4190.0</v>
       </c>
       <c r="R16" s="5" t="s">
         <v>89</v>
       </c>
       <c r="S16" s="3">
-        <v>6890</v>
+        <v>6890.0</v>
       </c>
       <c r="T16" s="3">
-        <v>3800</v>
+        <v>3800.0</v>
       </c>
       <c r="U16" s="3">
-        <v>8.6991999999999994</v>
+        <v>8.6992</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>133</v>
@@ -2180,12 +1889,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15.75" customHeight="1">
+    <row r="17">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="B17" s="4">
-        <v>42786</v>
+        <v>42786.0</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>124</v>
@@ -2206,7 +1915,7 @@
         <v>112</v>
       </c>
       <c r="I17" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>135</v>
@@ -2221,29 +1930,29 @@
         <v>136</v>
       </c>
       <c r="N17" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O17" s="3">
-        <v>1550</v>
-      </c>
-      <c r="P17" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1550.0</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="1"/>
+        <v>6 hours</v>
       </c>
       <c r="Q17" s="3">
-        <v>4000</v>
+        <v>4000.0</v>
       </c>
       <c r="R17" s="5" t="s">
         <v>64</v>
       </c>
       <c r="S17" s="3">
-        <v>7200</v>
+        <v>7200.0</v>
       </c>
       <c r="T17" s="3">
-        <v>3600</v>
+        <v>3600.0</v>
       </c>
       <c r="U17" s="3">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>137</v>
@@ -2255,12 +1964,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.75" customHeight="1">
+    <row r="18">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="B18" s="4">
-        <v>42791</v>
+        <v>42791.0</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>24</v>
@@ -2281,7 +1990,7 @@
         <v>103</v>
       </c>
       <c r="I18" s="3">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>139</v>
@@ -2296,29 +2005,29 @@
         <v>141</v>
       </c>
       <c r="N18" s="3">
-        <v>800</v>
+        <v>800.0</v>
       </c>
       <c r="O18" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P18" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1700.0</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="1"/>
+        <v>9 hours</v>
       </c>
       <c r="Q18" s="3">
-        <v>2600</v>
+        <v>2600.0</v>
       </c>
       <c r="R18" s="5" t="s">
         <v>107</v>
       </c>
       <c r="S18" s="3">
-        <v>5700</v>
+        <v>5700.0</v>
       </c>
       <c r="T18" s="3">
-        <v>4000</v>
+        <v>4000.0</v>
       </c>
       <c r="U18" s="3">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>142</v>
@@ -2330,12 +2039,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15.75" customHeight="1">
+    <row r="19">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="B19" s="4">
-        <v>42799</v>
+        <v>42799.0</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>24</v>
@@ -2356,7 +2065,7 @@
         <v>144</v>
       </c>
       <c r="I19" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>145</v>
@@ -2371,14 +2080,14 @@
         <v>146</v>
       </c>
       <c r="N19" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O19" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P19" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+        <v>1500.0</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="1"/>
+        <v>5.5 hours</v>
       </c>
       <c r="Q19" s="9">
         <v>2961.29</v>
@@ -2390,10 +2099,10 @@
         <v>5414.86</v>
       </c>
       <c r="T19" s="9">
-        <v>2447.1799999999998</v>
+        <v>2447.18</v>
       </c>
       <c r="U19" s="11">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="V19" s="3" t="s">
         <v>147</v>
@@ -2405,12 +2114,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15.75" customHeight="1">
+    <row r="20">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="B20" s="4">
-        <v>42812</v>
+        <v>42812.0</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>150</v>
@@ -2431,7 +2140,7 @@
         <v>153</v>
       </c>
       <c r="I20" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>154</v>
@@ -2446,25 +2155,25 @@
         <v>156</v>
       </c>
       <c r="N20" s="3">
-        <v>1000</v>
+        <v>1000.0</v>
       </c>
       <c r="O20" s="3">
-        <v>1400</v>
+        <v>1400.0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>157</v>
       </c>
       <c r="Q20" s="3">
-        <v>4000</v>
+        <v>4000.0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>157</v>
       </c>
       <c r="S20" s="3">
-        <v>5000</v>
+        <v>5000.0</v>
       </c>
       <c r="T20" s="3">
-        <v>1500</v>
+        <v>1500.0</v>
       </c>
       <c r="U20" s="3">
         <v>3.5</v>
@@ -2479,12 +2188,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15.75" customHeight="1">
+    <row r="21">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="B21" s="4">
-        <v>42813</v>
+        <v>42813.0</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>150</v>
@@ -2505,7 +2214,7 @@
         <v>161</v>
       </c>
       <c r="I21" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>162</v>
@@ -2520,25 +2229,25 @@
         <v>164</v>
       </c>
       <c r="N21" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O21" s="3">
-        <v>1450</v>
+        <v>1450.0</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>165</v>
       </c>
       <c r="Q21" s="3">
-        <v>4000</v>
+        <v>4000.0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>165</v>
       </c>
       <c r="S21" s="3">
-        <v>5700</v>
+        <v>5700.0</v>
       </c>
       <c r="T21" s="3">
-        <v>2095</v>
+        <v>2095.0</v>
       </c>
       <c r="U21" s="3">
         <v>4.87</v>
@@ -2553,12 +2262,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15.75" customHeight="1">
+    <row r="22">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="B22" s="4">
-        <v>42820</v>
+        <v>42820.0</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>52</v>
@@ -2579,7 +2288,7 @@
         <v>68</v>
       </c>
       <c r="I22" s="3">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>169</v>
@@ -2594,25 +2303,25 @@
         <v>171</v>
       </c>
       <c r="N22" s="3">
-        <v>950</v>
+        <v>950.0</v>
       </c>
       <c r="O22" s="3">
-        <v>1550</v>
+        <v>1550.0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="Q22" s="3">
-        <v>4300</v>
+        <v>4300.0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="S22" s="3">
-        <v>6500</v>
+        <v>6500.0</v>
       </c>
       <c r="T22" s="12">
-        <v>3800</v>
+        <v>3800.0</v>
       </c>
       <c r="U22" s="3">
         <v>7.6</v>
@@ -2627,25 +2336,3032 @@
         <v>173</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="4">
+        <v>42828.0</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="N23" s="3">
+        <v>1050.0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>1650.0</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q23" s="3">
+        <f>S23-T23</f>
+        <v>5400</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S23" s="8">
+        <v>10080.0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>4680.0</v>
+      </c>
+      <c r="U23" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X23" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="13"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="13"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="13"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="13"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="13"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="13"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="13"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="13"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="13"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="13"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="13"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="13"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="13"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="13"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="13"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="13"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="13"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="13"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="13"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="13"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="13"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="13"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="13"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="13"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="13"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="13"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="13"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="13"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="13"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="13"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="13"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="13"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="13"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="13"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="13"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="13"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="13"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="13"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="13"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="13"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="13"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="13"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="13"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="13"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="13"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="13"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="13"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="13"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="13"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="13"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="13"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="13"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="13"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="13"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="13"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="13"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="13"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="13"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="13"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="13"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="13"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="13"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="13"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="13"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="13"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="13"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="13"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="13"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="13"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="13"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="13"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="13"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="13"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="13"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="13"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="13"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="13"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="13"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="13"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="13"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="13"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="13"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="13"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="13"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="13"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="13"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="13"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="13"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="13"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="13"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="13"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="13"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="13"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="13"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="13"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="13"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="13"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="13"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="13"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="13"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="13"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="13"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="13"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="13"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="13"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="13"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="13"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="13"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="13"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="13"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="13"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="13"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="13"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="13"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="13"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="13"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="13"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="13"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="13"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="13"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="13"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="13"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="13"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="13"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="13"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="13"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="13"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="13"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="13"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="13"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="13"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="13"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="13"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="13"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="13"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="13"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="13"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="13"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="13"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="13"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="13"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="13"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="13"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="13"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="13"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="13"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="13"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="13"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="13"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="13"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="13"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="13"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="13"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="13"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="13"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="13"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="13"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="13"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="13"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="13"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="13"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="13"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="13"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="13"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="13"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="13"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="13"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="13"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="13"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="13"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="13"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="13"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="13"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="13"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="13"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="13"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="13"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="13"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="13"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="13"/>
+    </row>
+    <row r="204">
+      <c r="B204" s="13"/>
+    </row>
+    <row r="205">
+      <c r="B205" s="13"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="13"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="13"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="13"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="13"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="13"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="13"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="13"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="13"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="13"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="13"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="13"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="13"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="13"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="13"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="13"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="13"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="13"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="13"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="13"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="13"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="13"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="13"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="13"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="13"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="13"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="13"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="13"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="13"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="13"/>
+    </row>
+    <row r="235">
+      <c r="B235" s="13"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="13"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="13"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="13"/>
+    </row>
+    <row r="239">
+      <c r="B239" s="13"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="13"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="13"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="13"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="13"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="13"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="13"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="13"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="13"/>
+    </row>
+    <row r="248">
+      <c r="B248" s="13"/>
+    </row>
+    <row r="249">
+      <c r="B249" s="13"/>
+    </row>
+    <row r="250">
+      <c r="B250" s="13"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="13"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="13"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="13"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="13"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="13"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="13"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="13"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="13"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="13"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="13"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="13"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="13"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="13"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="13"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="13"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="13"/>
+    </row>
+    <row r="267">
+      <c r="B267" s="13"/>
+    </row>
+    <row r="268">
+      <c r="B268" s="13"/>
+    </row>
+    <row r="269">
+      <c r="B269" s="13"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="13"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="13"/>
+    </row>
+    <row r="272">
+      <c r="B272" s="13"/>
+    </row>
+    <row r="273">
+      <c r="B273" s="13"/>
+    </row>
+    <row r="274">
+      <c r="B274" s="13"/>
+    </row>
+    <row r="275">
+      <c r="B275" s="13"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="13"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="13"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="13"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="13"/>
+    </row>
+    <row r="280">
+      <c r="B280" s="13"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="13"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="13"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="13"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="13"/>
+    </row>
+    <row r="285">
+      <c r="B285" s="13"/>
+    </row>
+    <row r="286">
+      <c r="B286" s="13"/>
+    </row>
+    <row r="287">
+      <c r="B287" s="13"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="13"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="13"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="13"/>
+    </row>
+    <row r="291">
+      <c r="B291" s="13"/>
+    </row>
+    <row r="292">
+      <c r="B292" s="13"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="13"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="13"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="13"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="13"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="13"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="13"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="13"/>
+    </row>
+    <row r="300">
+      <c r="B300" s="13"/>
+    </row>
+    <row r="301">
+      <c r="B301" s="13"/>
+    </row>
+    <row r="302">
+      <c r="B302" s="13"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="13"/>
+    </row>
+    <row r="304">
+      <c r="B304" s="13"/>
+    </row>
+    <row r="305">
+      <c r="B305" s="13"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="13"/>
+    </row>
+    <row r="307">
+      <c r="B307" s="13"/>
+    </row>
+    <row r="308">
+      <c r="B308" s="13"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="13"/>
+    </row>
+    <row r="310">
+      <c r="B310" s="13"/>
+    </row>
+    <row r="311">
+      <c r="B311" s="13"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="13"/>
+    </row>
+    <row r="313">
+      <c r="B313" s="13"/>
+    </row>
+    <row r="314">
+      <c r="B314" s="13"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="13"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="13"/>
+    </row>
+    <row r="317">
+      <c r="B317" s="13"/>
+    </row>
+    <row r="318">
+      <c r="B318" s="13"/>
+    </row>
+    <row r="319">
+      <c r="B319" s="13"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="13"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="13"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="13"/>
+    </row>
+    <row r="323">
+      <c r="B323" s="13"/>
+    </row>
+    <row r="324">
+      <c r="B324" s="13"/>
+    </row>
+    <row r="325">
+      <c r="B325" s="13"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="13"/>
+    </row>
+    <row r="327">
+      <c r="B327" s="13"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="13"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="13"/>
+    </row>
+    <row r="330">
+      <c r="B330" s="13"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="13"/>
+    </row>
+    <row r="332">
+      <c r="B332" s="13"/>
+    </row>
+    <row r="333">
+      <c r="B333" s="13"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="13"/>
+    </row>
+    <row r="335">
+      <c r="B335" s="13"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="13"/>
+    </row>
+    <row r="337">
+      <c r="B337" s="13"/>
+    </row>
+    <row r="338">
+      <c r="B338" s="13"/>
+    </row>
+    <row r="339">
+      <c r="B339" s="13"/>
+    </row>
+    <row r="340">
+      <c r="B340" s="13"/>
+    </row>
+    <row r="341">
+      <c r="B341" s="13"/>
+    </row>
+    <row r="342">
+      <c r="B342" s="13"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="13"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="13"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="13"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="13"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="13"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="13"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="13"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="13"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="13"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="13"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="13"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="13"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="13"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="13"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="13"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="13"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="13"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="13"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="13"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="13"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="13"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="13"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="13"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="13"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="13"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="13"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="13"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="13"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="13"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="13"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="13"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="13"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="13"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="13"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="13"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="13"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="13"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="13"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="13"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="13"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="13"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="13"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="13"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="13"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="13"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="13"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="13"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="13"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="13"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="13"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="13"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="13"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="13"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="13"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="13"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="13"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="13"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="13"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="13"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="13"/>
+    </row>
+    <row r="403">
+      <c r="B403" s="13"/>
+    </row>
+    <row r="404">
+      <c r="B404" s="13"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="13"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="13"/>
+    </row>
+    <row r="407">
+      <c r="B407" s="13"/>
+    </row>
+    <row r="408">
+      <c r="B408" s="13"/>
+    </row>
+    <row r="409">
+      <c r="B409" s="13"/>
+    </row>
+    <row r="410">
+      <c r="B410" s="13"/>
+    </row>
+    <row r="411">
+      <c r="B411" s="13"/>
+    </row>
+    <row r="412">
+      <c r="B412" s="13"/>
+    </row>
+    <row r="413">
+      <c r="B413" s="13"/>
+    </row>
+    <row r="414">
+      <c r="B414" s="13"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="13"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="13"/>
+    </row>
+    <row r="417">
+      <c r="B417" s="13"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="13"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="13"/>
+    </row>
+    <row r="420">
+      <c r="B420" s="13"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="13"/>
+    </row>
+    <row r="422">
+      <c r="B422" s="13"/>
+    </row>
+    <row r="423">
+      <c r="B423" s="13"/>
+    </row>
+    <row r="424">
+      <c r="B424" s="13"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="13"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="13"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="13"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="13"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="13"/>
+    </row>
+    <row r="430">
+      <c r="B430" s="13"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="13"/>
+    </row>
+    <row r="432">
+      <c r="B432" s="13"/>
+    </row>
+    <row r="433">
+      <c r="B433" s="13"/>
+    </row>
+    <row r="434">
+      <c r="B434" s="13"/>
+    </row>
+    <row r="435">
+      <c r="B435" s="13"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="13"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="13"/>
+    </row>
+    <row r="438">
+      <c r="B438" s="13"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="13"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="13"/>
+    </row>
+    <row r="441">
+      <c r="B441" s="13"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="13"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="13"/>
+    </row>
+    <row r="444">
+      <c r="B444" s="13"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="13"/>
+    </row>
+    <row r="446">
+      <c r="B446" s="13"/>
+    </row>
+    <row r="447">
+      <c r="B447" s="13"/>
+    </row>
+    <row r="448">
+      <c r="B448" s="13"/>
+    </row>
+    <row r="449">
+      <c r="B449" s="13"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="13"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="13"/>
+    </row>
+    <row r="452">
+      <c r="B452" s="13"/>
+    </row>
+    <row r="453">
+      <c r="B453" s="13"/>
+    </row>
+    <row r="454">
+      <c r="B454" s="13"/>
+    </row>
+    <row r="455">
+      <c r="B455" s="13"/>
+    </row>
+    <row r="456">
+      <c r="B456" s="13"/>
+    </row>
+    <row r="457">
+      <c r="B457" s="13"/>
+    </row>
+    <row r="458">
+      <c r="B458" s="13"/>
+    </row>
+    <row r="459">
+      <c r="B459" s="13"/>
+    </row>
+    <row r="460">
+      <c r="B460" s="13"/>
+    </row>
+    <row r="461">
+      <c r="B461" s="13"/>
+    </row>
+    <row r="462">
+      <c r="B462" s="13"/>
+    </row>
+    <row r="463">
+      <c r="B463" s="13"/>
+    </row>
+    <row r="464">
+      <c r="B464" s="13"/>
+    </row>
+    <row r="465">
+      <c r="B465" s="13"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="13"/>
+    </row>
+    <row r="467">
+      <c r="B467" s="13"/>
+    </row>
+    <row r="468">
+      <c r="B468" s="13"/>
+    </row>
+    <row r="469">
+      <c r="B469" s="13"/>
+    </row>
+    <row r="470">
+      <c r="B470" s="13"/>
+    </row>
+    <row r="471">
+      <c r="B471" s="13"/>
+    </row>
+    <row r="472">
+      <c r="B472" s="13"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="13"/>
+    </row>
+    <row r="474">
+      <c r="B474" s="13"/>
+    </row>
+    <row r="475">
+      <c r="B475" s="13"/>
+    </row>
+    <row r="476">
+      <c r="B476" s="13"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="13"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="13"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="13"/>
+    </row>
+    <row r="480">
+      <c r="B480" s="13"/>
+    </row>
+    <row r="481">
+      <c r="B481" s="13"/>
+    </row>
+    <row r="482">
+      <c r="B482" s="13"/>
+    </row>
+    <row r="483">
+      <c r="B483" s="13"/>
+    </row>
+    <row r="484">
+      <c r="B484" s="13"/>
+    </row>
+    <row r="485">
+      <c r="B485" s="13"/>
+    </row>
+    <row r="486">
+      <c r="B486" s="13"/>
+    </row>
+    <row r="487">
+      <c r="B487" s="13"/>
+    </row>
+    <row r="488">
+      <c r="B488" s="13"/>
+    </row>
+    <row r="489">
+      <c r="B489" s="13"/>
+    </row>
+    <row r="490">
+      <c r="B490" s="13"/>
+    </row>
+    <row r="491">
+      <c r="B491" s="13"/>
+    </row>
+    <row r="492">
+      <c r="B492" s="13"/>
+    </row>
+    <row r="493">
+      <c r="B493" s="13"/>
+    </row>
+    <row r="494">
+      <c r="B494" s="13"/>
+    </row>
+    <row r="495">
+      <c r="B495" s="13"/>
+    </row>
+    <row r="496">
+      <c r="B496" s="13"/>
+    </row>
+    <row r="497">
+      <c r="B497" s="13"/>
+    </row>
+    <row r="498">
+      <c r="B498" s="13"/>
+    </row>
+    <row r="499">
+      <c r="B499" s="13"/>
+    </row>
+    <row r="500">
+      <c r="B500" s="13"/>
+    </row>
+    <row r="501">
+      <c r="B501" s="13"/>
+    </row>
+    <row r="502">
+      <c r="B502" s="13"/>
+    </row>
+    <row r="503">
+      <c r="B503" s="13"/>
+    </row>
+    <row r="504">
+      <c r="B504" s="13"/>
+    </row>
+    <row r="505">
+      <c r="B505" s="13"/>
+    </row>
+    <row r="506">
+      <c r="B506" s="13"/>
+    </row>
+    <row r="507">
+      <c r="B507" s="13"/>
+    </row>
+    <row r="508">
+      <c r="B508" s="13"/>
+    </row>
+    <row r="509">
+      <c r="B509" s="13"/>
+    </row>
+    <row r="510">
+      <c r="B510" s="13"/>
+    </row>
+    <row r="511">
+      <c r="B511" s="13"/>
+    </row>
+    <row r="512">
+      <c r="B512" s="13"/>
+    </row>
+    <row r="513">
+      <c r="B513" s="13"/>
+    </row>
+    <row r="514">
+      <c r="B514" s="13"/>
+    </row>
+    <row r="515">
+      <c r="B515" s="13"/>
+    </row>
+    <row r="516">
+      <c r="B516" s="13"/>
+    </row>
+    <row r="517">
+      <c r="B517" s="13"/>
+    </row>
+    <row r="518">
+      <c r="B518" s="13"/>
+    </row>
+    <row r="519">
+      <c r="B519" s="13"/>
+    </row>
+    <row r="520">
+      <c r="B520" s="13"/>
+    </row>
+    <row r="521">
+      <c r="B521" s="13"/>
+    </row>
+    <row r="522">
+      <c r="B522" s="13"/>
+    </row>
+    <row r="523">
+      <c r="B523" s="13"/>
+    </row>
+    <row r="524">
+      <c r="B524" s="13"/>
+    </row>
+    <row r="525">
+      <c r="B525" s="13"/>
+    </row>
+    <row r="526">
+      <c r="B526" s="13"/>
+    </row>
+    <row r="527">
+      <c r="B527" s="13"/>
+    </row>
+    <row r="528">
+      <c r="B528" s="13"/>
+    </row>
+    <row r="529">
+      <c r="B529" s="13"/>
+    </row>
+    <row r="530">
+      <c r="B530" s="13"/>
+    </row>
+    <row r="531">
+      <c r="B531" s="13"/>
+    </row>
+    <row r="532">
+      <c r="B532" s="13"/>
+    </row>
+    <row r="533">
+      <c r="B533" s="13"/>
+    </row>
+    <row r="534">
+      <c r="B534" s="13"/>
+    </row>
+    <row r="535">
+      <c r="B535" s="13"/>
+    </row>
+    <row r="536">
+      <c r="B536" s="13"/>
+    </row>
+    <row r="537">
+      <c r="B537" s="13"/>
+    </row>
+    <row r="538">
+      <c r="B538" s="13"/>
+    </row>
+    <row r="539">
+      <c r="B539" s="13"/>
+    </row>
+    <row r="540">
+      <c r="B540" s="13"/>
+    </row>
+    <row r="541">
+      <c r="B541" s="13"/>
+    </row>
+    <row r="542">
+      <c r="B542" s="13"/>
+    </row>
+    <row r="543">
+      <c r="B543" s="13"/>
+    </row>
+    <row r="544">
+      <c r="B544" s="13"/>
+    </row>
+    <row r="545">
+      <c r="B545" s="13"/>
+    </row>
+    <row r="546">
+      <c r="B546" s="13"/>
+    </row>
+    <row r="547">
+      <c r="B547" s="13"/>
+    </row>
+    <row r="548">
+      <c r="B548" s="13"/>
+    </row>
+    <row r="549">
+      <c r="B549" s="13"/>
+    </row>
+    <row r="550">
+      <c r="B550" s="13"/>
+    </row>
+    <row r="551">
+      <c r="B551" s="13"/>
+    </row>
+    <row r="552">
+      <c r="B552" s="13"/>
+    </row>
+    <row r="553">
+      <c r="B553" s="13"/>
+    </row>
+    <row r="554">
+      <c r="B554" s="13"/>
+    </row>
+    <row r="555">
+      <c r="B555" s="13"/>
+    </row>
+    <row r="556">
+      <c r="B556" s="13"/>
+    </row>
+    <row r="557">
+      <c r="B557" s="13"/>
+    </row>
+    <row r="558">
+      <c r="B558" s="13"/>
+    </row>
+    <row r="559">
+      <c r="B559" s="13"/>
+    </row>
+    <row r="560">
+      <c r="B560" s="13"/>
+    </row>
+    <row r="561">
+      <c r="B561" s="13"/>
+    </row>
+    <row r="562">
+      <c r="B562" s="13"/>
+    </row>
+    <row r="563">
+      <c r="B563" s="13"/>
+    </row>
+    <row r="564">
+      <c r="B564" s="13"/>
+    </row>
+    <row r="565">
+      <c r="B565" s="13"/>
+    </row>
+    <row r="566">
+      <c r="B566" s="13"/>
+    </row>
+    <row r="567">
+      <c r="B567" s="13"/>
+    </row>
+    <row r="568">
+      <c r="B568" s="13"/>
+    </row>
+    <row r="569">
+      <c r="B569" s="13"/>
+    </row>
+    <row r="570">
+      <c r="B570" s="13"/>
+    </row>
+    <row r="571">
+      <c r="B571" s="13"/>
+    </row>
+    <row r="572">
+      <c r="B572" s="13"/>
+    </row>
+    <row r="573">
+      <c r="B573" s="13"/>
+    </row>
+    <row r="574">
+      <c r="B574" s="13"/>
+    </row>
+    <row r="575">
+      <c r="B575" s="13"/>
+    </row>
+    <row r="576">
+      <c r="B576" s="13"/>
+    </row>
+    <row r="577">
+      <c r="B577" s="13"/>
+    </row>
+    <row r="578">
+      <c r="B578" s="13"/>
+    </row>
+    <row r="579">
+      <c r="B579" s="13"/>
+    </row>
+    <row r="580">
+      <c r="B580" s="13"/>
+    </row>
+    <row r="581">
+      <c r="B581" s="13"/>
+    </row>
+    <row r="582">
+      <c r="B582" s="13"/>
+    </row>
+    <row r="583">
+      <c r="B583" s="13"/>
+    </row>
+    <row r="584">
+      <c r="B584" s="13"/>
+    </row>
+    <row r="585">
+      <c r="B585" s="13"/>
+    </row>
+    <row r="586">
+      <c r="B586" s="13"/>
+    </row>
+    <row r="587">
+      <c r="B587" s="13"/>
+    </row>
+    <row r="588">
+      <c r="B588" s="13"/>
+    </row>
+    <row r="589">
+      <c r="B589" s="13"/>
+    </row>
+    <row r="590">
+      <c r="B590" s="13"/>
+    </row>
+    <row r="591">
+      <c r="B591" s="13"/>
+    </row>
+    <row r="592">
+      <c r="B592" s="13"/>
+    </row>
+    <row r="593">
+      <c r="B593" s="13"/>
+    </row>
+    <row r="594">
+      <c r="B594" s="13"/>
+    </row>
+    <row r="595">
+      <c r="B595" s="13"/>
+    </row>
+    <row r="596">
+      <c r="B596" s="13"/>
+    </row>
+    <row r="597">
+      <c r="B597" s="13"/>
+    </row>
+    <row r="598">
+      <c r="B598" s="13"/>
+    </row>
+    <row r="599">
+      <c r="B599" s="13"/>
+    </row>
+    <row r="600">
+      <c r="B600" s="13"/>
+    </row>
+    <row r="601">
+      <c r="B601" s="13"/>
+    </row>
+    <row r="602">
+      <c r="B602" s="13"/>
+    </row>
+    <row r="603">
+      <c r="B603" s="13"/>
+    </row>
+    <row r="604">
+      <c r="B604" s="13"/>
+    </row>
+    <row r="605">
+      <c r="B605" s="13"/>
+    </row>
+    <row r="606">
+      <c r="B606" s="13"/>
+    </row>
+    <row r="607">
+      <c r="B607" s="13"/>
+    </row>
+    <row r="608">
+      <c r="B608" s="13"/>
+    </row>
+    <row r="609">
+      <c r="B609" s="13"/>
+    </row>
+    <row r="610">
+      <c r="B610" s="13"/>
+    </row>
+    <row r="611">
+      <c r="B611" s="13"/>
+    </row>
+    <row r="612">
+      <c r="B612" s="13"/>
+    </row>
+    <row r="613">
+      <c r="B613" s="13"/>
+    </row>
+    <row r="614">
+      <c r="B614" s="13"/>
+    </row>
+    <row r="615">
+      <c r="B615" s="13"/>
+    </row>
+    <row r="616">
+      <c r="B616" s="13"/>
+    </row>
+    <row r="617">
+      <c r="B617" s="13"/>
+    </row>
+    <row r="618">
+      <c r="B618" s="13"/>
+    </row>
+    <row r="619">
+      <c r="B619" s="13"/>
+    </row>
+    <row r="620">
+      <c r="B620" s="13"/>
+    </row>
+    <row r="621">
+      <c r="B621" s="13"/>
+    </row>
+    <row r="622">
+      <c r="B622" s="13"/>
+    </row>
+    <row r="623">
+      <c r="B623" s="13"/>
+    </row>
+    <row r="624">
+      <c r="B624" s="13"/>
+    </row>
+    <row r="625">
+      <c r="B625" s="13"/>
+    </row>
+    <row r="626">
+      <c r="B626" s="13"/>
+    </row>
+    <row r="627">
+      <c r="B627" s="13"/>
+    </row>
+    <row r="628">
+      <c r="B628" s="13"/>
+    </row>
+    <row r="629">
+      <c r="B629" s="13"/>
+    </row>
+    <row r="630">
+      <c r="B630" s="13"/>
+    </row>
+    <row r="631">
+      <c r="B631" s="13"/>
+    </row>
+    <row r="632">
+      <c r="B632" s="13"/>
+    </row>
+    <row r="633">
+      <c r="B633" s="13"/>
+    </row>
+    <row r="634">
+      <c r="B634" s="13"/>
+    </row>
+    <row r="635">
+      <c r="B635" s="13"/>
+    </row>
+    <row r="636">
+      <c r="B636" s="13"/>
+    </row>
+    <row r="637">
+      <c r="B637" s="13"/>
+    </row>
+    <row r="638">
+      <c r="B638" s="13"/>
+    </row>
+    <row r="639">
+      <c r="B639" s="13"/>
+    </row>
+    <row r="640">
+      <c r="B640" s="13"/>
+    </row>
+    <row r="641">
+      <c r="B641" s="13"/>
+    </row>
+    <row r="642">
+      <c r="B642" s="13"/>
+    </row>
+    <row r="643">
+      <c r="B643" s="13"/>
+    </row>
+    <row r="644">
+      <c r="B644" s="13"/>
+    </row>
+    <row r="645">
+      <c r="B645" s="13"/>
+    </row>
+    <row r="646">
+      <c r="B646" s="13"/>
+    </row>
+    <row r="647">
+      <c r="B647" s="13"/>
+    </row>
+    <row r="648">
+      <c r="B648" s="13"/>
+    </row>
+    <row r="649">
+      <c r="B649" s="13"/>
+    </row>
+    <row r="650">
+      <c r="B650" s="13"/>
+    </row>
+    <row r="651">
+      <c r="B651" s="13"/>
+    </row>
+    <row r="652">
+      <c r="B652" s="13"/>
+    </row>
+    <row r="653">
+      <c r="B653" s="13"/>
+    </row>
+    <row r="654">
+      <c r="B654" s="13"/>
+    </row>
+    <row r="655">
+      <c r="B655" s="13"/>
+    </row>
+    <row r="656">
+      <c r="B656" s="13"/>
+    </row>
+    <row r="657">
+      <c r="B657" s="13"/>
+    </row>
+    <row r="658">
+      <c r="B658" s="13"/>
+    </row>
+    <row r="659">
+      <c r="B659" s="13"/>
+    </row>
+    <row r="660">
+      <c r="B660" s="13"/>
+    </row>
+    <row r="661">
+      <c r="B661" s="13"/>
+    </row>
+    <row r="662">
+      <c r="B662" s="13"/>
+    </row>
+    <row r="663">
+      <c r="B663" s="13"/>
+    </row>
+    <row r="664">
+      <c r="B664" s="13"/>
+    </row>
+    <row r="665">
+      <c r="B665" s="13"/>
+    </row>
+    <row r="666">
+      <c r="B666" s="13"/>
+    </row>
+    <row r="667">
+      <c r="B667" s="13"/>
+    </row>
+    <row r="668">
+      <c r="B668" s="13"/>
+    </row>
+    <row r="669">
+      <c r="B669" s="13"/>
+    </row>
+    <row r="670">
+      <c r="B670" s="13"/>
+    </row>
+    <row r="671">
+      <c r="B671" s="13"/>
+    </row>
+    <row r="672">
+      <c r="B672" s="13"/>
+    </row>
+    <row r="673">
+      <c r="B673" s="13"/>
+    </row>
+    <row r="674">
+      <c r="B674" s="13"/>
+    </row>
+    <row r="675">
+      <c r="B675" s="13"/>
+    </row>
+    <row r="676">
+      <c r="B676" s="13"/>
+    </row>
+    <row r="677">
+      <c r="B677" s="13"/>
+    </row>
+    <row r="678">
+      <c r="B678" s="13"/>
+    </row>
+    <row r="679">
+      <c r="B679" s="13"/>
+    </row>
+    <row r="680">
+      <c r="B680" s="13"/>
+    </row>
+    <row r="681">
+      <c r="B681" s="13"/>
+    </row>
+    <row r="682">
+      <c r="B682" s="13"/>
+    </row>
+    <row r="683">
+      <c r="B683" s="13"/>
+    </row>
+    <row r="684">
+      <c r="B684" s="13"/>
+    </row>
+    <row r="685">
+      <c r="B685" s="13"/>
+    </row>
+    <row r="686">
+      <c r="B686" s="13"/>
+    </row>
+    <row r="687">
+      <c r="B687" s="13"/>
+    </row>
+    <row r="688">
+      <c r="B688" s="13"/>
+    </row>
+    <row r="689">
+      <c r="B689" s="13"/>
+    </row>
+    <row r="690">
+      <c r="B690" s="13"/>
+    </row>
+    <row r="691">
+      <c r="B691" s="13"/>
+    </row>
+    <row r="692">
+      <c r="B692" s="13"/>
+    </row>
+    <row r="693">
+      <c r="B693" s="13"/>
+    </row>
+    <row r="694">
+      <c r="B694" s="13"/>
+    </row>
+    <row r="695">
+      <c r="B695" s="13"/>
+    </row>
+    <row r="696">
+      <c r="B696" s="13"/>
+    </row>
+    <row r="697">
+      <c r="B697" s="13"/>
+    </row>
+    <row r="698">
+      <c r="B698" s="13"/>
+    </row>
+    <row r="699">
+      <c r="B699" s="13"/>
+    </row>
+    <row r="700">
+      <c r="B700" s="13"/>
+    </row>
+    <row r="701">
+      <c r="B701" s="13"/>
+    </row>
+    <row r="702">
+      <c r="B702" s="13"/>
+    </row>
+    <row r="703">
+      <c r="B703" s="13"/>
+    </row>
+    <row r="704">
+      <c r="B704" s="13"/>
+    </row>
+    <row r="705">
+      <c r="B705" s="13"/>
+    </row>
+    <row r="706">
+      <c r="B706" s="13"/>
+    </row>
+    <row r="707">
+      <c r="B707" s="13"/>
+    </row>
+    <row r="708">
+      <c r="B708" s="13"/>
+    </row>
+    <row r="709">
+      <c r="B709" s="13"/>
+    </row>
+    <row r="710">
+      <c r="B710" s="13"/>
+    </row>
+    <row r="711">
+      <c r="B711" s="13"/>
+    </row>
+    <row r="712">
+      <c r="B712" s="13"/>
+    </row>
+    <row r="713">
+      <c r="B713" s="13"/>
+    </row>
+    <row r="714">
+      <c r="B714" s="13"/>
+    </row>
+    <row r="715">
+      <c r="B715" s="13"/>
+    </row>
+    <row r="716">
+      <c r="B716" s="13"/>
+    </row>
+    <row r="717">
+      <c r="B717" s="13"/>
+    </row>
+    <row r="718">
+      <c r="B718" s="13"/>
+    </row>
+    <row r="719">
+      <c r="B719" s="13"/>
+    </row>
+    <row r="720">
+      <c r="B720" s="13"/>
+    </row>
+    <row r="721">
+      <c r="B721" s="13"/>
+    </row>
+    <row r="722">
+      <c r="B722" s="13"/>
+    </row>
+    <row r="723">
+      <c r="B723" s="13"/>
+    </row>
+    <row r="724">
+      <c r="B724" s="13"/>
+    </row>
+    <row r="725">
+      <c r="B725" s="13"/>
+    </row>
+    <row r="726">
+      <c r="B726" s="13"/>
+    </row>
+    <row r="727">
+      <c r="B727" s="13"/>
+    </row>
+    <row r="728">
+      <c r="B728" s="13"/>
+    </row>
+    <row r="729">
+      <c r="B729" s="13"/>
+    </row>
+    <row r="730">
+      <c r="B730" s="13"/>
+    </row>
+    <row r="731">
+      <c r="B731" s="13"/>
+    </row>
+    <row r="732">
+      <c r="B732" s="13"/>
+    </row>
+    <row r="733">
+      <c r="B733" s="13"/>
+    </row>
+    <row r="734">
+      <c r="B734" s="13"/>
+    </row>
+    <row r="735">
+      <c r="B735" s="13"/>
+    </row>
+    <row r="736">
+      <c r="B736" s="13"/>
+    </row>
+    <row r="737">
+      <c r="B737" s="13"/>
+    </row>
+    <row r="738">
+      <c r="B738" s="13"/>
+    </row>
+    <row r="739">
+      <c r="B739" s="13"/>
+    </row>
+    <row r="740">
+      <c r="B740" s="13"/>
+    </row>
+    <row r="741">
+      <c r="B741" s="13"/>
+    </row>
+    <row r="742">
+      <c r="B742" s="13"/>
+    </row>
+    <row r="743">
+      <c r="B743" s="13"/>
+    </row>
+    <row r="744">
+      <c r="B744" s="13"/>
+    </row>
+    <row r="745">
+      <c r="B745" s="13"/>
+    </row>
+    <row r="746">
+      <c r="B746" s="13"/>
+    </row>
+    <row r="747">
+      <c r="B747" s="13"/>
+    </row>
+    <row r="748">
+      <c r="B748" s="13"/>
+    </row>
+    <row r="749">
+      <c r="B749" s="13"/>
+    </row>
+    <row r="750">
+      <c r="B750" s="13"/>
+    </row>
+    <row r="751">
+      <c r="B751" s="13"/>
+    </row>
+    <row r="752">
+      <c r="B752" s="13"/>
+    </row>
+    <row r="753">
+      <c r="B753" s="13"/>
+    </row>
+    <row r="754">
+      <c r="B754" s="13"/>
+    </row>
+    <row r="755">
+      <c r="B755" s="13"/>
+    </row>
+    <row r="756">
+      <c r="B756" s="13"/>
+    </row>
+    <row r="757">
+      <c r="B757" s="13"/>
+    </row>
+    <row r="758">
+      <c r="B758" s="13"/>
+    </row>
+    <row r="759">
+      <c r="B759" s="13"/>
+    </row>
+    <row r="760">
+      <c r="B760" s="13"/>
+    </row>
+    <row r="761">
+      <c r="B761" s="13"/>
+    </row>
+    <row r="762">
+      <c r="B762" s="13"/>
+    </row>
+    <row r="763">
+      <c r="B763" s="13"/>
+    </row>
+    <row r="764">
+      <c r="B764" s="13"/>
+    </row>
+    <row r="765">
+      <c r="B765" s="13"/>
+    </row>
+    <row r="766">
+      <c r="B766" s="13"/>
+    </row>
+    <row r="767">
+      <c r="B767" s="13"/>
+    </row>
+    <row r="768">
+      <c r="B768" s="13"/>
+    </row>
+    <row r="769">
+      <c r="B769" s="13"/>
+    </row>
+    <row r="770">
+      <c r="B770" s="13"/>
+    </row>
+    <row r="771">
+      <c r="B771" s="13"/>
+    </row>
+    <row r="772">
+      <c r="B772" s="13"/>
+    </row>
+    <row r="773">
+      <c r="B773" s="13"/>
+    </row>
+    <row r="774">
+      <c r="B774" s="13"/>
+    </row>
+    <row r="775">
+      <c r="B775" s="13"/>
+    </row>
+    <row r="776">
+      <c r="B776" s="13"/>
+    </row>
+    <row r="777">
+      <c r="B777" s="13"/>
+    </row>
+    <row r="778">
+      <c r="B778" s="13"/>
+    </row>
+    <row r="779">
+      <c r="B779" s="13"/>
+    </row>
+    <row r="780">
+      <c r="B780" s="13"/>
+    </row>
+    <row r="781">
+      <c r="B781" s="13"/>
+    </row>
+    <row r="782">
+      <c r="B782" s="13"/>
+    </row>
+    <row r="783">
+      <c r="B783" s="13"/>
+    </row>
+    <row r="784">
+      <c r="B784" s="13"/>
+    </row>
+    <row r="785">
+      <c r="B785" s="13"/>
+    </row>
+    <row r="786">
+      <c r="B786" s="13"/>
+    </row>
+    <row r="787">
+      <c r="B787" s="13"/>
+    </row>
+    <row r="788">
+      <c r="B788" s="13"/>
+    </row>
+    <row r="789">
+      <c r="B789" s="13"/>
+    </row>
+    <row r="790">
+      <c r="B790" s="13"/>
+    </row>
+    <row r="791">
+      <c r="B791" s="13"/>
+    </row>
+    <row r="792">
+      <c r="B792" s="13"/>
+    </row>
+    <row r="793">
+      <c r="B793" s="13"/>
+    </row>
+    <row r="794">
+      <c r="B794" s="13"/>
+    </row>
+    <row r="795">
+      <c r="B795" s="13"/>
+    </row>
+    <row r="796">
+      <c r="B796" s="13"/>
+    </row>
+    <row r="797">
+      <c r="B797" s="13"/>
+    </row>
+    <row r="798">
+      <c r="B798" s="13"/>
+    </row>
+    <row r="799">
+      <c r="B799" s="13"/>
+    </row>
+    <row r="800">
+      <c r="B800" s="13"/>
+    </row>
+    <row r="801">
+      <c r="B801" s="13"/>
+    </row>
+    <row r="802">
+      <c r="B802" s="13"/>
+    </row>
+    <row r="803">
+      <c r="B803" s="13"/>
+    </row>
+    <row r="804">
+      <c r="B804" s="13"/>
+    </row>
+    <row r="805">
+      <c r="B805" s="13"/>
+    </row>
+    <row r="806">
+      <c r="B806" s="13"/>
+    </row>
+    <row r="807">
+      <c r="B807" s="13"/>
+    </row>
+    <row r="808">
+      <c r="B808" s="13"/>
+    </row>
+    <row r="809">
+      <c r="B809" s="13"/>
+    </row>
+    <row r="810">
+      <c r="B810" s="13"/>
+    </row>
+    <row r="811">
+      <c r="B811" s="13"/>
+    </row>
+    <row r="812">
+      <c r="B812" s="13"/>
+    </row>
+    <row r="813">
+      <c r="B813" s="13"/>
+    </row>
+    <row r="814">
+      <c r="B814" s="13"/>
+    </row>
+    <row r="815">
+      <c r="B815" s="13"/>
+    </row>
+    <row r="816">
+      <c r="B816" s="13"/>
+    </row>
+    <row r="817">
+      <c r="B817" s="13"/>
+    </row>
+    <row r="818">
+      <c r="B818" s="13"/>
+    </row>
+    <row r="819">
+      <c r="B819" s="13"/>
+    </row>
+    <row r="820">
+      <c r="B820" s="13"/>
+    </row>
+    <row r="821">
+      <c r="B821" s="13"/>
+    </row>
+    <row r="822">
+      <c r="B822" s="13"/>
+    </row>
+    <row r="823">
+      <c r="B823" s="13"/>
+    </row>
+    <row r="824">
+      <c r="B824" s="13"/>
+    </row>
+    <row r="825">
+      <c r="B825" s="13"/>
+    </row>
+    <row r="826">
+      <c r="B826" s="13"/>
+    </row>
+    <row r="827">
+      <c r="B827" s="13"/>
+    </row>
+    <row r="828">
+      <c r="B828" s="13"/>
+    </row>
+    <row r="829">
+      <c r="B829" s="13"/>
+    </row>
+    <row r="830">
+      <c r="B830" s="13"/>
+    </row>
+    <row r="831">
+      <c r="B831" s="13"/>
+    </row>
+    <row r="832">
+      <c r="B832" s="13"/>
+    </row>
+    <row r="833">
+      <c r="B833" s="13"/>
+    </row>
+    <row r="834">
+      <c r="B834" s="13"/>
+    </row>
+    <row r="835">
+      <c r="B835" s="13"/>
+    </row>
+    <row r="836">
+      <c r="B836" s="13"/>
+    </row>
+    <row r="837">
+      <c r="B837" s="13"/>
+    </row>
+    <row r="838">
+      <c r="B838" s="13"/>
+    </row>
+    <row r="839">
+      <c r="B839" s="13"/>
+    </row>
+    <row r="840">
+      <c r="B840" s="13"/>
+    </row>
+    <row r="841">
+      <c r="B841" s="13"/>
+    </row>
+    <row r="842">
+      <c r="B842" s="13"/>
+    </row>
+    <row r="843">
+      <c r="B843" s="13"/>
+    </row>
+    <row r="844">
+      <c r="B844" s="13"/>
+    </row>
+    <row r="845">
+      <c r="B845" s="13"/>
+    </row>
+    <row r="846">
+      <c r="B846" s="13"/>
+    </row>
+    <row r="847">
+      <c r="B847" s="13"/>
+    </row>
+    <row r="848">
+      <c r="B848" s="13"/>
+    </row>
+    <row r="849">
+      <c r="B849" s="13"/>
+    </row>
+    <row r="850">
+      <c r="B850" s="13"/>
+    </row>
+    <row r="851">
+      <c r="B851" s="13"/>
+    </row>
+    <row r="852">
+      <c r="B852" s="13"/>
+    </row>
+    <row r="853">
+      <c r="B853" s="13"/>
+    </row>
+    <row r="854">
+      <c r="B854" s="13"/>
+    </row>
+    <row r="855">
+      <c r="B855" s="13"/>
+    </row>
+    <row r="856">
+      <c r="B856" s="13"/>
+    </row>
+    <row r="857">
+      <c r="B857" s="13"/>
+    </row>
+    <row r="858">
+      <c r="B858" s="13"/>
+    </row>
+    <row r="859">
+      <c r="B859" s="13"/>
+    </row>
+    <row r="860">
+      <c r="B860" s="13"/>
+    </row>
+    <row r="861">
+      <c r="B861" s="13"/>
+    </row>
+    <row r="862">
+      <c r="B862" s="13"/>
+    </row>
+    <row r="863">
+      <c r="B863" s="13"/>
+    </row>
+    <row r="864">
+      <c r="B864" s="13"/>
+    </row>
+    <row r="865">
+      <c r="B865" s="13"/>
+    </row>
+    <row r="866">
+      <c r="B866" s="13"/>
+    </row>
+    <row r="867">
+      <c r="B867" s="13"/>
+    </row>
+    <row r="868">
+      <c r="B868" s="13"/>
+    </row>
+    <row r="869">
+      <c r="B869" s="13"/>
+    </row>
+    <row r="870">
+      <c r="B870" s="13"/>
+    </row>
+    <row r="871">
+      <c r="B871" s="13"/>
+    </row>
+    <row r="872">
+      <c r="B872" s="13"/>
+    </row>
+    <row r="873">
+      <c r="B873" s="13"/>
+    </row>
+    <row r="874">
+      <c r="B874" s="13"/>
+    </row>
+    <row r="875">
+      <c r="B875" s="13"/>
+    </row>
+    <row r="876">
+      <c r="B876" s="13"/>
+    </row>
+    <row r="877">
+      <c r="B877" s="13"/>
+    </row>
+    <row r="878">
+      <c r="B878" s="13"/>
+    </row>
+    <row r="879">
+      <c r="B879" s="13"/>
+    </row>
+    <row r="880">
+      <c r="B880" s="13"/>
+    </row>
+    <row r="881">
+      <c r="B881" s="13"/>
+    </row>
+    <row r="882">
+      <c r="B882" s="13"/>
+    </row>
+    <row r="883">
+      <c r="B883" s="13"/>
+    </row>
+    <row r="884">
+      <c r="B884" s="13"/>
+    </row>
+    <row r="885">
+      <c r="B885" s="13"/>
+    </row>
+    <row r="886">
+      <c r="B886" s="13"/>
+    </row>
+    <row r="887">
+      <c r="B887" s="13"/>
+    </row>
+    <row r="888">
+      <c r="B888" s="13"/>
+    </row>
+    <row r="889">
+      <c r="B889" s="13"/>
+    </row>
+    <row r="890">
+      <c r="B890" s="13"/>
+    </row>
+    <row r="891">
+      <c r="B891" s="13"/>
+    </row>
+    <row r="892">
+      <c r="B892" s="13"/>
+    </row>
+    <row r="893">
+      <c r="B893" s="13"/>
+    </row>
+    <row r="894">
+      <c r="B894" s="13"/>
+    </row>
+    <row r="895">
+      <c r="B895" s="13"/>
+    </row>
+    <row r="896">
+      <c r="B896" s="13"/>
+    </row>
+    <row r="897">
+      <c r="B897" s="13"/>
+    </row>
+    <row r="898">
+      <c r="B898" s="13"/>
+    </row>
+    <row r="899">
+      <c r="B899" s="13"/>
+    </row>
+    <row r="900">
+      <c r="B900" s="13"/>
+    </row>
+    <row r="901">
+      <c r="B901" s="13"/>
+    </row>
+    <row r="902">
+      <c r="B902" s="13"/>
+    </row>
+    <row r="903">
+      <c r="B903" s="13"/>
+    </row>
+    <row r="904">
+      <c r="B904" s="13"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="13"/>
+    </row>
+    <row r="906">
+      <c r="B906" s="13"/>
+    </row>
+    <row r="907">
+      <c r="B907" s="13"/>
+    </row>
+    <row r="908">
+      <c r="B908" s="13"/>
+    </row>
+    <row r="909">
+      <c r="B909" s="13"/>
+    </row>
+    <row r="910">
+      <c r="B910" s="13"/>
+    </row>
+    <row r="911">
+      <c r="B911" s="13"/>
+    </row>
+    <row r="912">
+      <c r="B912" s="13"/>
+    </row>
+    <row r="913">
+      <c r="B913" s="13"/>
+    </row>
+    <row r="914">
+      <c r="B914" s="13"/>
+    </row>
+    <row r="915">
+      <c r="B915" s="13"/>
+    </row>
+    <row r="916">
+      <c r="B916" s="13"/>
+    </row>
+    <row r="917">
+      <c r="B917" s="13"/>
+    </row>
+    <row r="918">
+      <c r="B918" s="13"/>
+    </row>
+    <row r="919">
+      <c r="B919" s="13"/>
+    </row>
+    <row r="920">
+      <c r="B920" s="13"/>
+    </row>
+    <row r="921">
+      <c r="B921" s="13"/>
+    </row>
+    <row r="922">
+      <c r="B922" s="13"/>
+    </row>
+    <row r="923">
+      <c r="B923" s="13"/>
+    </row>
+    <row r="924">
+      <c r="B924" s="13"/>
+    </row>
+    <row r="925">
+      <c r="B925" s="13"/>
+    </row>
+    <row r="926">
+      <c r="B926" s="13"/>
+    </row>
+    <row r="927">
+      <c r="B927" s="13"/>
+    </row>
+    <row r="928">
+      <c r="B928" s="13"/>
+    </row>
+    <row r="929">
+      <c r="B929" s="13"/>
+    </row>
+    <row r="930">
+      <c r="B930" s="13"/>
+    </row>
+    <row r="931">
+      <c r="B931" s="13"/>
+    </row>
+    <row r="932">
+      <c r="B932" s="13"/>
+    </row>
+    <row r="933">
+      <c r="B933" s="13"/>
+    </row>
+    <row r="934">
+      <c r="B934" s="13"/>
+    </row>
+    <row r="935">
+      <c r="B935" s="13"/>
+    </row>
+    <row r="936">
+      <c r="B936" s="13"/>
+    </row>
+    <row r="937">
+      <c r="B937" s="13"/>
+    </row>
+    <row r="938">
+      <c r="B938" s="13"/>
+    </row>
+    <row r="939">
+      <c r="B939" s="13"/>
+    </row>
+    <row r="940">
+      <c r="B940" s="13"/>
+    </row>
+    <row r="941">
+      <c r="B941" s="13"/>
+    </row>
+    <row r="942">
+      <c r="B942" s="13"/>
+    </row>
+    <row r="943">
+      <c r="B943" s="13"/>
+    </row>
+    <row r="944">
+      <c r="B944" s="13"/>
+    </row>
+    <row r="945">
+      <c r="B945" s="13"/>
+    </row>
+    <row r="946">
+      <c r="B946" s="13"/>
+    </row>
+    <row r="947">
+      <c r="B947" s="13"/>
+    </row>
+    <row r="948">
+      <c r="B948" s="13"/>
+    </row>
+    <row r="949">
+      <c r="B949" s="13"/>
+    </row>
+    <row r="950">
+      <c r="B950" s="13"/>
+    </row>
+    <row r="951">
+      <c r="B951" s="13"/>
+    </row>
+    <row r="952">
+      <c r="B952" s="13"/>
+    </row>
+    <row r="953">
+      <c r="B953" s="13"/>
+    </row>
+    <row r="954">
+      <c r="B954" s="13"/>
+    </row>
+    <row r="955">
+      <c r="B955" s="13"/>
+    </row>
+    <row r="956">
+      <c r="B956" s="13"/>
+    </row>
+    <row r="957">
+      <c r="B957" s="13"/>
+    </row>
+    <row r="958">
+      <c r="B958" s="13"/>
+    </row>
+    <row r="959">
+      <c r="B959" s="13"/>
+    </row>
+    <row r="960">
+      <c r="B960" s="13"/>
+    </row>
+    <row r="961">
+      <c r="B961" s="13"/>
+    </row>
+    <row r="962">
+      <c r="B962" s="13"/>
+    </row>
+    <row r="963">
+      <c r="B963" s="13"/>
+    </row>
+    <row r="964">
+      <c r="B964" s="13"/>
+    </row>
+    <row r="965">
+      <c r="B965" s="13"/>
+    </row>
+    <row r="966">
+      <c r="B966" s="13"/>
+    </row>
+    <row r="967">
+      <c r="B967" s="13"/>
+    </row>
+    <row r="968">
+      <c r="B968" s="13"/>
+    </row>
+    <row r="969">
+      <c r="B969" s="13"/>
+    </row>
+    <row r="970">
+      <c r="B970" s="13"/>
+    </row>
+    <row r="971">
+      <c r="B971" s="13"/>
+    </row>
+    <row r="972">
+      <c r="B972" s="13"/>
+    </row>
+    <row r="973">
+      <c r="B973" s="13"/>
+    </row>
+    <row r="974">
+      <c r="B974" s="13"/>
+    </row>
+    <row r="975">
+      <c r="B975" s="13"/>
+    </row>
+    <row r="976">
+      <c r="B976" s="13"/>
+    </row>
+    <row r="977">
+      <c r="B977" s="13"/>
+    </row>
+    <row r="978">
+      <c r="B978" s="13"/>
+    </row>
+    <row r="979">
+      <c r="B979" s="13"/>
+    </row>
+    <row r="980">
+      <c r="B980" s="13"/>
+    </row>
+    <row r="981">
+      <c r="B981" s="13"/>
+    </row>
+    <row r="982">
+      <c r="B982" s="13"/>
+    </row>
+    <row r="983">
+      <c r="B983" s="13"/>
+    </row>
+    <row r="984">
+      <c r="B984" s="13"/>
+    </row>
+    <row r="985">
+      <c r="B985" s="13"/>
+    </row>
+    <row r="986">
+      <c r="B986" s="13"/>
+    </row>
+    <row r="987">
+      <c r="B987" s="13"/>
+    </row>
+    <row r="988">
+      <c r="B988" s="13"/>
+    </row>
+    <row r="989">
+      <c r="B989" s="13"/>
+    </row>
+    <row r="990">
+      <c r="B990" s="13"/>
+    </row>
+    <row r="991">
+      <c r="B991" s="13"/>
+    </row>
+    <row r="992">
+      <c r="B992" s="13"/>
+    </row>
+    <row r="993">
+      <c r="B993" s="13"/>
+    </row>
+    <row r="994">
+      <c r="B994" s="13"/>
+    </row>
+    <row r="995">
+      <c r="B995" s="13"/>
+    </row>
+    <row r="996">
+      <c r="B996" s="13"/>
+    </row>
+    <row r="997">
+      <c r="B997" s="13"/>
+    </row>
+    <row r="998">
+      <c r="B998" s="13"/>
+    </row>
+    <row r="999">
+      <c r="B999" s="13"/>
+    </row>
+    <row r="1000">
+      <c r="B1000" s="13"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="X2" r:id="rId1"/>
-    <hyperlink ref="X4" r:id="rId2"/>
-    <hyperlink ref="X7" r:id="rId3"/>
-    <hyperlink ref="X9" r:id="rId4"/>
-    <hyperlink ref="X10" r:id="rId5"/>
-    <hyperlink ref="X11" r:id="rId6"/>
-    <hyperlink ref="X12" r:id="rId7"/>
-    <hyperlink ref="X14" r:id="rId8"/>
-    <hyperlink ref="X15" r:id="rId9"/>
-    <hyperlink ref="X16" r:id="rId10"/>
-    <hyperlink ref="X17" r:id="rId11"/>
-    <hyperlink ref="X18" r:id="rId12"/>
-    <hyperlink ref="X19" r:id="rId13"/>
-    <hyperlink ref="X20" r:id="rId14"/>
-    <hyperlink ref="X21" r:id="rId15"/>
-    <hyperlink ref="X22" r:id="rId16"/>
+    <hyperlink r:id="rId1" ref="X2"/>
+    <hyperlink r:id="rId2" ref="X4"/>
+    <hyperlink r:id="rId3" ref="X7"/>
+    <hyperlink r:id="rId4" ref="X9"/>
+    <hyperlink r:id="rId5" ref="X10"/>
+    <hyperlink r:id="rId6" ref="X11"/>
+    <hyperlink r:id="rId7" ref="X12"/>
+    <hyperlink r:id="rId8" ref="X14"/>
+    <hyperlink r:id="rId9" ref="X15"/>
+    <hyperlink r:id="rId10" ref="X16"/>
+    <hyperlink r:id="rId11" ref="X17"/>
+    <hyperlink r:id="rId12" ref="X18"/>
+    <hyperlink r:id="rId13" ref="X19"/>
+    <hyperlink r:id="rId14" ref="X20"/>
+    <hyperlink r:id="rId15" ref="X21"/>
+    <hyperlink r:id="rId16" ref="X22"/>
+    <hyperlink r:id="rId17" ref="X23"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="186">
   <si>
     <t>id</t>
   </si>
@@ -542,6 +542,33 @@
   </si>
   <si>
     <t>https://goo.gl/photos/vbwSH4zZGAcjfWYZ7</t>
+  </si>
+  <si>
+    <t>tatoosh range</t>
+  </si>
+  <si>
+    <t>narada falls trailhead</t>
+  </si>
+  <si>
+    <t>party cloudy</t>
+  </si>
+  <si>
+    <t>Ben, Liberty</t>
+  </si>
+  <si>
+    <t>We toured up to reflection lakes and then up towards the castle. Once at the saddle below the saddle Ben and I decided to drop southwards to the backside of the castle. Liberty did not feel physical up to it so he descened safely solo down our skin track route. Ben and I skiied above 800 feet down the back side and then transitioned at the top of a steep short pitch; we could have continued descending another 300-400 feet but we had never been in this zone so we kept it cautious.We skinned back up to the ridge towards the Castle but veered east and ascended up to spot below a peak that lies east of the castle. From here we skiied back towards Louise Lake. This was a great ~1500 ft run with 6-8 inches of fresh spring powder. We then transitioned and skinned back along the road towards the trailhead.</t>
+  </si>
+  <si>
+    <t>few wet slides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare a strategy if one of your group members isn't able to continue on with the group. Carefully consider if it is safe for one of your group members to descend alone. </t>
+  </si>
+  <si>
+    <t>castle loop (tatoosh)</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/e83Js2wy2StPAqsD7</t>
   </si>
 </sst>
 </file>
@@ -2412,7 +2439,78 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="13"/>
+      <c r="A24" s="3">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="4">
+        <v>42834.0</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1550.0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>4500.0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S24" s="3">
+        <v>6400.0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>2800.0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="X24" s="6" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="13"/>
@@ -5361,7 +5459,8 @@
     <hyperlink r:id="rId15" ref="X21"/>
     <hyperlink r:id="rId16" ref="X22"/>
     <hyperlink r:id="rId17" ref="X23"/>
+    <hyperlink r:id="rId18" ref="X24"/>
   </hyperlinks>
-  <drawing r:id="rId18"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="185">
   <si>
     <t>id</t>
   </si>
@@ -544,9 +544,6 @@
     <t>https://goo.gl/photos/vbwSH4zZGAcjfWYZ7</t>
   </si>
   <si>
-    <t>tatoosh range</t>
-  </si>
-  <si>
     <t>narada falls trailhead</t>
   </si>
   <si>
@@ -565,10 +562,10 @@
     <t xml:space="preserve">Prepare a strategy if one of your group members isn't able to continue on with the group. Carefully consider if it is safe for one of your group members to descend alone. </t>
   </si>
   <si>
-    <t>castle loop (tatoosh)</t>
-  </si>
-  <si>
-    <t>https://goo.gl/photos/e83Js2wy2StPAqsD7</t>
+    <t>castle loop (tatoosh range)</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/6z9abe5WkQdCqYTY8</t>
   </si>
 </sst>
 </file>
@@ -578,7 +575,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -607,6 +604,9 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Arimo"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="4">
@@ -640,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment/>
     </xf>
@@ -674,6 +674,9 @@
       <alignment/>
     </xf>
     <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -2446,10 +2449,10 @@
         <v>42834.0</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
@@ -2458,25 +2461,25 @@
         <v>44</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="I24" s="3">
         <v>3.0</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N24" s="3">
         <v>1000.0</v>
@@ -2503,2942 +2506,2942 @@
         <v>6.6</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="X24" s="6" t="s">
-        <v>185</v>
+      <c r="X24" s="13" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13"/>
+      <c r="B25" s="14"/>
     </row>
     <row r="26">
-      <c r="B26" s="13"/>
+      <c r="B26" s="14"/>
     </row>
     <row r="27">
-      <c r="B27" s="13"/>
+      <c r="B27" s="14"/>
     </row>
     <row r="28">
-      <c r="B28" s="13"/>
+      <c r="B28" s="14"/>
     </row>
     <row r="29">
-      <c r="B29" s="13"/>
+      <c r="B29" s="14"/>
     </row>
     <row r="30">
-      <c r="B30" s="13"/>
+      <c r="B30" s="14"/>
     </row>
     <row r="31">
-      <c r="B31" s="13"/>
+      <c r="B31" s="14"/>
     </row>
     <row r="32">
-      <c r="B32" s="13"/>
+      <c r="B32" s="14"/>
     </row>
     <row r="33">
-      <c r="B33" s="13"/>
+      <c r="B33" s="14"/>
     </row>
     <row r="34">
-      <c r="B34" s="13"/>
+      <c r="B34" s="14"/>
     </row>
     <row r="35">
-      <c r="B35" s="13"/>
+      <c r="B35" s="14"/>
     </row>
     <row r="36">
-      <c r="B36" s="13"/>
+      <c r="B36" s="14"/>
     </row>
     <row r="37">
-      <c r="B37" s="13"/>
+      <c r="B37" s="14"/>
     </row>
     <row r="38">
-      <c r="B38" s="13"/>
+      <c r="B38" s="14"/>
     </row>
     <row r="39">
-      <c r="B39" s="13"/>
+      <c r="B39" s="14"/>
     </row>
     <row r="40">
-      <c r="B40" s="13"/>
+      <c r="B40" s="14"/>
     </row>
     <row r="41">
-      <c r="B41" s="13"/>
+      <c r="B41" s="14"/>
     </row>
     <row r="42">
-      <c r="B42" s="13"/>
+      <c r="B42" s="14"/>
     </row>
     <row r="43">
-      <c r="B43" s="13"/>
+      <c r="B43" s="14"/>
     </row>
     <row r="44">
-      <c r="B44" s="13"/>
+      <c r="B44" s="14"/>
     </row>
     <row r="45">
-      <c r="B45" s="13"/>
+      <c r="B45" s="14"/>
     </row>
     <row r="46">
-      <c r="B46" s="13"/>
+      <c r="B46" s="14"/>
     </row>
     <row r="47">
-      <c r="B47" s="13"/>
+      <c r="B47" s="14"/>
     </row>
     <row r="48">
-      <c r="B48" s="13"/>
+      <c r="B48" s="14"/>
     </row>
     <row r="49">
-      <c r="B49" s="13"/>
+      <c r="B49" s="14"/>
     </row>
     <row r="50">
-      <c r="B50" s="13"/>
+      <c r="B50" s="14"/>
     </row>
     <row r="51">
-      <c r="B51" s="13"/>
+      <c r="B51" s="14"/>
     </row>
     <row r="52">
-      <c r="B52" s="13"/>
+      <c r="B52" s="14"/>
     </row>
     <row r="53">
-      <c r="B53" s="13"/>
+      <c r="B53" s="14"/>
     </row>
     <row r="54">
-      <c r="B54" s="13"/>
+      <c r="B54" s="14"/>
     </row>
     <row r="55">
-      <c r="B55" s="13"/>
+      <c r="B55" s="14"/>
     </row>
     <row r="56">
-      <c r="B56" s="13"/>
+      <c r="B56" s="14"/>
     </row>
     <row r="57">
-      <c r="B57" s="13"/>
+      <c r="B57" s="14"/>
     </row>
     <row r="58">
-      <c r="B58" s="13"/>
+      <c r="B58" s="14"/>
     </row>
     <row r="59">
-      <c r="B59" s="13"/>
+      <c r="B59" s="14"/>
     </row>
     <row r="60">
-      <c r="B60" s="13"/>
+      <c r="B60" s="14"/>
     </row>
     <row r="61">
-      <c r="B61" s="13"/>
+      <c r="B61" s="14"/>
     </row>
     <row r="62">
-      <c r="B62" s="13"/>
+      <c r="B62" s="14"/>
     </row>
     <row r="63">
-      <c r="B63" s="13"/>
+      <c r="B63" s="14"/>
     </row>
     <row r="64">
-      <c r="B64" s="13"/>
+      <c r="B64" s="14"/>
     </row>
     <row r="65">
-      <c r="B65" s="13"/>
+      <c r="B65" s="14"/>
     </row>
     <row r="66">
-      <c r="B66" s="13"/>
+      <c r="B66" s="14"/>
     </row>
     <row r="67">
-      <c r="B67" s="13"/>
+      <c r="B67" s="14"/>
     </row>
     <row r="68">
-      <c r="B68" s="13"/>
+      <c r="B68" s="14"/>
     </row>
     <row r="69">
-      <c r="B69" s="13"/>
+      <c r="B69" s="14"/>
     </row>
     <row r="70">
-      <c r="B70" s="13"/>
+      <c r="B70" s="14"/>
     </row>
     <row r="71">
-      <c r="B71" s="13"/>
+      <c r="B71" s="14"/>
     </row>
     <row r="72">
-      <c r="B72" s="13"/>
+      <c r="B72" s="14"/>
     </row>
     <row r="73">
-      <c r="B73" s="13"/>
+      <c r="B73" s="14"/>
     </row>
     <row r="74">
-      <c r="B74" s="13"/>
+      <c r="B74" s="14"/>
     </row>
     <row r="75">
-      <c r="B75" s="13"/>
+      <c r="B75" s="14"/>
     </row>
     <row r="76">
-      <c r="B76" s="13"/>
+      <c r="B76" s="14"/>
     </row>
     <row r="77">
-      <c r="B77" s="13"/>
+      <c r="B77" s="14"/>
     </row>
     <row r="78">
-      <c r="B78" s="13"/>
+      <c r="B78" s="14"/>
     </row>
     <row r="79">
-      <c r="B79" s="13"/>
+      <c r="B79" s="14"/>
     </row>
     <row r="80">
-      <c r="B80" s="13"/>
+      <c r="B80" s="14"/>
     </row>
     <row r="81">
-      <c r="B81" s="13"/>
+      <c r="B81" s="14"/>
     </row>
     <row r="82">
-      <c r="B82" s="13"/>
+      <c r="B82" s="14"/>
     </row>
     <row r="83">
-      <c r="B83" s="13"/>
+      <c r="B83" s="14"/>
     </row>
     <row r="84">
-      <c r="B84" s="13"/>
+      <c r="B84" s="14"/>
     </row>
     <row r="85">
-      <c r="B85" s="13"/>
+      <c r="B85" s="14"/>
     </row>
     <row r="86">
-      <c r="B86" s="13"/>
+      <c r="B86" s="14"/>
     </row>
     <row r="87">
-      <c r="B87" s="13"/>
+      <c r="B87" s="14"/>
     </row>
     <row r="88">
-      <c r="B88" s="13"/>
+      <c r="B88" s="14"/>
     </row>
     <row r="89">
-      <c r="B89" s="13"/>
+      <c r="B89" s="14"/>
     </row>
     <row r="90">
-      <c r="B90" s="13"/>
+      <c r="B90" s="14"/>
     </row>
     <row r="91">
-      <c r="B91" s="13"/>
+      <c r="B91" s="14"/>
     </row>
     <row r="92">
-      <c r="B92" s="13"/>
+      <c r="B92" s="14"/>
     </row>
     <row r="93">
-      <c r="B93" s="13"/>
+      <c r="B93" s="14"/>
     </row>
     <row r="94">
-      <c r="B94" s="13"/>
+      <c r="B94" s="14"/>
     </row>
     <row r="95">
-      <c r="B95" s="13"/>
+      <c r="B95" s="14"/>
     </row>
     <row r="96">
-      <c r="B96" s="13"/>
+      <c r="B96" s="14"/>
     </row>
     <row r="97">
-      <c r="B97" s="13"/>
+      <c r="B97" s="14"/>
     </row>
     <row r="98">
-      <c r="B98" s="13"/>
+      <c r="B98" s="14"/>
     </row>
     <row r="99">
-      <c r="B99" s="13"/>
+      <c r="B99" s="14"/>
     </row>
     <row r="100">
-      <c r="B100" s="13"/>
+      <c r="B100" s="14"/>
     </row>
     <row r="101">
-      <c r="B101" s="13"/>
+      <c r="B101" s="14"/>
     </row>
     <row r="102">
-      <c r="B102" s="13"/>
+      <c r="B102" s="14"/>
     </row>
     <row r="103">
-      <c r="B103" s="13"/>
+      <c r="B103" s="14"/>
     </row>
     <row r="104">
-      <c r="B104" s="13"/>
+      <c r="B104" s="14"/>
     </row>
     <row r="105">
-      <c r="B105" s="13"/>
+      <c r="B105" s="14"/>
     </row>
     <row r="106">
-      <c r="B106" s="13"/>
+      <c r="B106" s="14"/>
     </row>
     <row r="107">
-      <c r="B107" s="13"/>
+      <c r="B107" s="14"/>
     </row>
     <row r="108">
-      <c r="B108" s="13"/>
+      <c r="B108" s="14"/>
     </row>
     <row r="109">
-      <c r="B109" s="13"/>
+      <c r="B109" s="14"/>
     </row>
     <row r="110">
-      <c r="B110" s="13"/>
+      <c r="B110" s="14"/>
     </row>
     <row r="111">
-      <c r="B111" s="13"/>
+      <c r="B111" s="14"/>
     </row>
     <row r="112">
-      <c r="B112" s="13"/>
+      <c r="B112" s="14"/>
     </row>
     <row r="113">
-      <c r="B113" s="13"/>
+      <c r="B113" s="14"/>
     </row>
     <row r="114">
-      <c r="B114" s="13"/>
+      <c r="B114" s="14"/>
     </row>
     <row r="115">
-      <c r="B115" s="13"/>
+      <c r="B115" s="14"/>
     </row>
     <row r="116">
-      <c r="B116" s="13"/>
+      <c r="B116" s="14"/>
     </row>
     <row r="117">
-      <c r="B117" s="13"/>
+      <c r="B117" s="14"/>
     </row>
     <row r="118">
-      <c r="B118" s="13"/>
+      <c r="B118" s="14"/>
     </row>
     <row r="119">
-      <c r="B119" s="13"/>
+      <c r="B119" s="14"/>
     </row>
     <row r="120">
-      <c r="B120" s="13"/>
+      <c r="B120" s="14"/>
     </row>
     <row r="121">
-      <c r="B121" s="13"/>
+      <c r="B121" s="14"/>
     </row>
     <row r="122">
-      <c r="B122" s="13"/>
+      <c r="B122" s="14"/>
     </row>
     <row r="123">
-      <c r="B123" s="13"/>
+      <c r="B123" s="14"/>
     </row>
     <row r="124">
-      <c r="B124" s="13"/>
+      <c r="B124" s="14"/>
     </row>
     <row r="125">
-      <c r="B125" s="13"/>
+      <c r="B125" s="14"/>
     </row>
     <row r="126">
-      <c r="B126" s="13"/>
+      <c r="B126" s="14"/>
     </row>
     <row r="127">
-      <c r="B127" s="13"/>
+      <c r="B127" s="14"/>
     </row>
     <row r="128">
-      <c r="B128" s="13"/>
+      <c r="B128" s="14"/>
     </row>
     <row r="129">
-      <c r="B129" s="13"/>
+      <c r="B129" s="14"/>
     </row>
     <row r="130">
-      <c r="B130" s="13"/>
+      <c r="B130" s="14"/>
     </row>
     <row r="131">
-      <c r="B131" s="13"/>
+      <c r="B131" s="14"/>
     </row>
     <row r="132">
-      <c r="B132" s="13"/>
+      <c r="B132" s="14"/>
     </row>
     <row r="133">
-      <c r="B133" s="13"/>
+      <c r="B133" s="14"/>
     </row>
     <row r="134">
-      <c r="B134" s="13"/>
+      <c r="B134" s="14"/>
     </row>
     <row r="135">
-      <c r="B135" s="13"/>
+      <c r="B135" s="14"/>
     </row>
     <row r="136">
-      <c r="B136" s="13"/>
+      <c r="B136" s="14"/>
     </row>
     <row r="137">
-      <c r="B137" s="13"/>
+      <c r="B137" s="14"/>
     </row>
     <row r="138">
-      <c r="B138" s="13"/>
+      <c r="B138" s="14"/>
     </row>
     <row r="139">
-      <c r="B139" s="13"/>
+      <c r="B139" s="14"/>
     </row>
     <row r="140">
-      <c r="B140" s="13"/>
+      <c r="B140" s="14"/>
     </row>
     <row r="141">
-      <c r="B141" s="13"/>
+      <c r="B141" s="14"/>
     </row>
     <row r="142">
-      <c r="B142" s="13"/>
+      <c r="B142" s="14"/>
     </row>
     <row r="143">
-      <c r="B143" s="13"/>
+      <c r="B143" s="14"/>
     </row>
     <row r="144">
-      <c r="B144" s="13"/>
+      <c r="B144" s="14"/>
     </row>
     <row r="145">
-      <c r="B145" s="13"/>
+      <c r="B145" s="14"/>
     </row>
     <row r="146">
-      <c r="B146" s="13"/>
+      <c r="B146" s="14"/>
     </row>
     <row r="147">
-      <c r="B147" s="13"/>
+      <c r="B147" s="14"/>
     </row>
     <row r="148">
-      <c r="B148" s="13"/>
+      <c r="B148" s="14"/>
     </row>
     <row r="149">
-      <c r="B149" s="13"/>
+      <c r="B149" s="14"/>
     </row>
     <row r="150">
-      <c r="B150" s="13"/>
+      <c r="B150" s="14"/>
     </row>
     <row r="151">
-      <c r="B151" s="13"/>
+      <c r="B151" s="14"/>
     </row>
     <row r="152">
-      <c r="B152" s="13"/>
+      <c r="B152" s="14"/>
     </row>
     <row r="153">
-      <c r="B153" s="13"/>
+      <c r="B153" s="14"/>
     </row>
     <row r="154">
-      <c r="B154" s="13"/>
+      <c r="B154" s="14"/>
     </row>
     <row r="155">
-      <c r="B155" s="13"/>
+      <c r="B155" s="14"/>
     </row>
     <row r="156">
-      <c r="B156" s="13"/>
+      <c r="B156" s="14"/>
     </row>
     <row r="157">
-      <c r="B157" s="13"/>
+      <c r="B157" s="14"/>
     </row>
     <row r="158">
-      <c r="B158" s="13"/>
+      <c r="B158" s="14"/>
     </row>
     <row r="159">
-      <c r="B159" s="13"/>
+      <c r="B159" s="14"/>
     </row>
     <row r="160">
-      <c r="B160" s="13"/>
+      <c r="B160" s="14"/>
     </row>
     <row r="161">
-      <c r="B161" s="13"/>
+      <c r="B161" s="14"/>
     </row>
     <row r="162">
-      <c r="B162" s="13"/>
+      <c r="B162" s="14"/>
     </row>
     <row r="163">
-      <c r="B163" s="13"/>
+      <c r="B163" s="14"/>
     </row>
     <row r="164">
-      <c r="B164" s="13"/>
+      <c r="B164" s="14"/>
     </row>
     <row r="165">
-      <c r="B165" s="13"/>
+      <c r="B165" s="14"/>
     </row>
     <row r="166">
-      <c r="B166" s="13"/>
+      <c r="B166" s="14"/>
     </row>
     <row r="167">
-      <c r="B167" s="13"/>
+      <c r="B167" s="14"/>
     </row>
     <row r="168">
-      <c r="B168" s="13"/>
+      <c r="B168" s="14"/>
     </row>
     <row r="169">
-      <c r="B169" s="13"/>
+      <c r="B169" s="14"/>
     </row>
     <row r="170">
-      <c r="B170" s="13"/>
+      <c r="B170" s="14"/>
     </row>
     <row r="171">
-      <c r="B171" s="13"/>
+      <c r="B171" s="14"/>
     </row>
     <row r="172">
-      <c r="B172" s="13"/>
+      <c r="B172" s="14"/>
     </row>
     <row r="173">
-      <c r="B173" s="13"/>
+      <c r="B173" s="14"/>
     </row>
     <row r="174">
-      <c r="B174" s="13"/>
+      <c r="B174" s="14"/>
     </row>
     <row r="175">
-      <c r="B175" s="13"/>
+      <c r="B175" s="14"/>
     </row>
     <row r="176">
-      <c r="B176" s="13"/>
+      <c r="B176" s="14"/>
     </row>
     <row r="177">
-      <c r="B177" s="13"/>
+      <c r="B177" s="14"/>
     </row>
     <row r="178">
-      <c r="B178" s="13"/>
+      <c r="B178" s="14"/>
     </row>
     <row r="179">
-      <c r="B179" s="13"/>
+      <c r="B179" s="14"/>
     </row>
     <row r="180">
-      <c r="B180" s="13"/>
+      <c r="B180" s="14"/>
     </row>
     <row r="181">
-      <c r="B181" s="13"/>
+      <c r="B181" s="14"/>
     </row>
     <row r="182">
-      <c r="B182" s="13"/>
+      <c r="B182" s="14"/>
     </row>
     <row r="183">
-      <c r="B183" s="13"/>
+      <c r="B183" s="14"/>
     </row>
     <row r="184">
-      <c r="B184" s="13"/>
+      <c r="B184" s="14"/>
     </row>
     <row r="185">
-      <c r="B185" s="13"/>
+      <c r="B185" s="14"/>
     </row>
     <row r="186">
-      <c r="B186" s="13"/>
+      <c r="B186" s="14"/>
     </row>
     <row r="187">
-      <c r="B187" s="13"/>
+      <c r="B187" s="14"/>
     </row>
     <row r="188">
-      <c r="B188" s="13"/>
+      <c r="B188" s="14"/>
     </row>
     <row r="189">
-      <c r="B189" s="13"/>
+      <c r="B189" s="14"/>
     </row>
     <row r="190">
-      <c r="B190" s="13"/>
+      <c r="B190" s="14"/>
     </row>
     <row r="191">
-      <c r="B191" s="13"/>
+      <c r="B191" s="14"/>
     </row>
     <row r="192">
-      <c r="B192" s="13"/>
+      <c r="B192" s="14"/>
     </row>
     <row r="193">
-      <c r="B193" s="13"/>
+      <c r="B193" s="14"/>
     </row>
     <row r="194">
-      <c r="B194" s="13"/>
+      <c r="B194" s="14"/>
     </row>
     <row r="195">
-      <c r="B195" s="13"/>
+      <c r="B195" s="14"/>
     </row>
     <row r="196">
-      <c r="B196" s="13"/>
+      <c r="B196" s="14"/>
     </row>
     <row r="197">
-      <c r="B197" s="13"/>
+      <c r="B197" s="14"/>
     </row>
     <row r="198">
-      <c r="B198" s="13"/>
+      <c r="B198" s="14"/>
     </row>
     <row r="199">
-      <c r="B199" s="13"/>
+      <c r="B199" s="14"/>
     </row>
     <row r="200">
-      <c r="B200" s="13"/>
+      <c r="B200" s="14"/>
     </row>
     <row r="201">
-      <c r="B201" s="13"/>
+      <c r="B201" s="14"/>
     </row>
     <row r="202">
-      <c r="B202" s="13"/>
+      <c r="B202" s="14"/>
     </row>
     <row r="203">
-      <c r="B203" s="13"/>
+      <c r="B203" s="14"/>
     </row>
     <row r="204">
-      <c r="B204" s="13"/>
+      <c r="B204" s="14"/>
     </row>
     <row r="205">
-      <c r="B205" s="13"/>
+      <c r="B205" s="14"/>
     </row>
     <row r="206">
-      <c r="B206" s="13"/>
+      <c r="B206" s="14"/>
     </row>
     <row r="207">
-      <c r="B207" s="13"/>
+      <c r="B207" s="14"/>
     </row>
     <row r="208">
-      <c r="B208" s="13"/>
+      <c r="B208" s="14"/>
     </row>
     <row r="209">
-      <c r="B209" s="13"/>
+      <c r="B209" s="14"/>
     </row>
     <row r="210">
-      <c r="B210" s="13"/>
+      <c r="B210" s="14"/>
     </row>
     <row r="211">
-      <c r="B211" s="13"/>
+      <c r="B211" s="14"/>
     </row>
     <row r="212">
-      <c r="B212" s="13"/>
+      <c r="B212" s="14"/>
     </row>
     <row r="213">
-      <c r="B213" s="13"/>
+      <c r="B213" s="14"/>
     </row>
     <row r="214">
-      <c r="B214" s="13"/>
+      <c r="B214" s="14"/>
     </row>
     <row r="215">
-      <c r="B215" s="13"/>
+      <c r="B215" s="14"/>
     </row>
     <row r="216">
-      <c r="B216" s="13"/>
+      <c r="B216" s="14"/>
     </row>
     <row r="217">
-      <c r="B217" s="13"/>
+      <c r="B217" s="14"/>
     </row>
     <row r="218">
-      <c r="B218" s="13"/>
+      <c r="B218" s="14"/>
     </row>
     <row r="219">
-      <c r="B219" s="13"/>
+      <c r="B219" s="14"/>
     </row>
     <row r="220">
-      <c r="B220" s="13"/>
+      <c r="B220" s="14"/>
     </row>
     <row r="221">
-      <c r="B221" s="13"/>
+      <c r="B221" s="14"/>
     </row>
     <row r="222">
-      <c r="B222" s="13"/>
+      <c r="B222" s="14"/>
     </row>
     <row r="223">
-      <c r="B223" s="13"/>
+      <c r="B223" s="14"/>
     </row>
     <row r="224">
-      <c r="B224" s="13"/>
+      <c r="B224" s="14"/>
     </row>
     <row r="225">
-      <c r="B225" s="13"/>
+      <c r="B225" s="14"/>
     </row>
     <row r="226">
-      <c r="B226" s="13"/>
+      <c r="B226" s="14"/>
     </row>
     <row r="227">
-      <c r="B227" s="13"/>
+      <c r="B227" s="14"/>
     </row>
     <row r="228">
-      <c r="B228" s="13"/>
+      <c r="B228" s="14"/>
     </row>
     <row r="229">
-      <c r="B229" s="13"/>
+      <c r="B229" s="14"/>
     </row>
     <row r="230">
-      <c r="B230" s="13"/>
+      <c r="B230" s="14"/>
     </row>
     <row r="231">
-      <c r="B231" s="13"/>
+      <c r="B231" s="14"/>
     </row>
     <row r="232">
-      <c r="B232" s="13"/>
+      <c r="B232" s="14"/>
     </row>
     <row r="233">
-      <c r="B233" s="13"/>
+      <c r="B233" s="14"/>
     </row>
     <row r="234">
-      <c r="B234" s="13"/>
+      <c r="B234" s="14"/>
     </row>
     <row r="235">
-      <c r="B235" s="13"/>
+      <c r="B235" s="14"/>
     </row>
     <row r="236">
-      <c r="B236" s="13"/>
+      <c r="B236" s="14"/>
     </row>
     <row r="237">
-      <c r="B237" s="13"/>
+      <c r="B237" s="14"/>
     </row>
     <row r="238">
-      <c r="B238" s="13"/>
+      <c r="B238" s="14"/>
     </row>
     <row r="239">
-      <c r="B239" s="13"/>
+      <c r="B239" s="14"/>
     </row>
     <row r="240">
-      <c r="B240" s="13"/>
+      <c r="B240" s="14"/>
     </row>
     <row r="241">
-      <c r="B241" s="13"/>
+      <c r="B241" s="14"/>
     </row>
     <row r="242">
-      <c r="B242" s="13"/>
+      <c r="B242" s="14"/>
     </row>
     <row r="243">
-      <c r="B243" s="13"/>
+      <c r="B243" s="14"/>
     </row>
     <row r="244">
-      <c r="B244" s="13"/>
+      <c r="B244" s="14"/>
     </row>
     <row r="245">
-      <c r="B245" s="13"/>
+      <c r="B245" s="14"/>
     </row>
     <row r="246">
-      <c r="B246" s="13"/>
+      <c r="B246" s="14"/>
     </row>
     <row r="247">
-      <c r="B247" s="13"/>
+      <c r="B247" s="14"/>
     </row>
     <row r="248">
-      <c r="B248" s="13"/>
+      <c r="B248" s="14"/>
     </row>
     <row r="249">
-      <c r="B249" s="13"/>
+      <c r="B249" s="14"/>
     </row>
     <row r="250">
-      <c r="B250" s="13"/>
+      <c r="B250" s="14"/>
     </row>
     <row r="251">
-      <c r="B251" s="13"/>
+      <c r="B251" s="14"/>
     </row>
     <row r="252">
-      <c r="B252" s="13"/>
+      <c r="B252" s="14"/>
     </row>
     <row r="253">
-      <c r="B253" s="13"/>
+      <c r="B253" s="14"/>
     </row>
     <row r="254">
-      <c r="B254" s="13"/>
+      <c r="B254" s="14"/>
     </row>
     <row r="255">
-      <c r="B255" s="13"/>
+      <c r="B255" s="14"/>
     </row>
     <row r="256">
-      <c r="B256" s="13"/>
+      <c r="B256" s="14"/>
     </row>
     <row r="257">
-      <c r="B257" s="13"/>
+      <c r="B257" s="14"/>
     </row>
     <row r="258">
-      <c r="B258" s="13"/>
+      <c r="B258" s="14"/>
     </row>
     <row r="259">
-      <c r="B259" s="13"/>
+      <c r="B259" s="14"/>
     </row>
     <row r="260">
-      <c r="B260" s="13"/>
+      <c r="B260" s="14"/>
     </row>
     <row r="261">
-      <c r="B261" s="13"/>
+      <c r="B261" s="14"/>
     </row>
     <row r="262">
-      <c r="B262" s="13"/>
+      <c r="B262" s="14"/>
     </row>
     <row r="263">
-      <c r="B263" s="13"/>
+      <c r="B263" s="14"/>
     </row>
     <row r="264">
-      <c r="B264" s="13"/>
+      <c r="B264" s="14"/>
     </row>
     <row r="265">
-      <c r="B265" s="13"/>
+      <c r="B265" s="14"/>
     </row>
     <row r="266">
-      <c r="B266" s="13"/>
+      <c r="B266" s="14"/>
     </row>
     <row r="267">
-      <c r="B267" s="13"/>
+      <c r="B267" s="14"/>
     </row>
     <row r="268">
-      <c r="B268" s="13"/>
+      <c r="B268" s="14"/>
     </row>
     <row r="269">
-      <c r="B269" s="13"/>
+      <c r="B269" s="14"/>
     </row>
     <row r="270">
-      <c r="B270" s="13"/>
+      <c r="B270" s="14"/>
     </row>
     <row r="271">
-      <c r="B271" s="13"/>
+      <c r="B271" s="14"/>
     </row>
     <row r="272">
-      <c r="B272" s="13"/>
+      <c r="B272" s="14"/>
     </row>
     <row r="273">
-      <c r="B273" s="13"/>
+      <c r="B273" s="14"/>
     </row>
     <row r="274">
-      <c r="B274" s="13"/>
+      <c r="B274" s="14"/>
     </row>
     <row r="275">
-      <c r="B275" s="13"/>
+      <c r="B275" s="14"/>
     </row>
     <row r="276">
-      <c r="B276" s="13"/>
+      <c r="B276" s="14"/>
     </row>
     <row r="277">
-      <c r="B277" s="13"/>
+      <c r="B277" s="14"/>
     </row>
     <row r="278">
-      <c r="B278" s="13"/>
+      <c r="B278" s="14"/>
     </row>
     <row r="279">
-      <c r="B279" s="13"/>
+      <c r="B279" s="14"/>
     </row>
     <row r="280">
-      <c r="B280" s="13"/>
+      <c r="B280" s="14"/>
     </row>
     <row r="281">
-      <c r="B281" s="13"/>
+      <c r="B281" s="14"/>
     </row>
     <row r="282">
-      <c r="B282" s="13"/>
+      <c r="B282" s="14"/>
     </row>
     <row r="283">
-      <c r="B283" s="13"/>
+      <c r="B283" s="14"/>
     </row>
     <row r="284">
-      <c r="B284" s="13"/>
+      <c r="B284" s="14"/>
     </row>
     <row r="285">
-      <c r="B285" s="13"/>
+      <c r="B285" s="14"/>
     </row>
     <row r="286">
-      <c r="B286" s="13"/>
+      <c r="B286" s="14"/>
     </row>
     <row r="287">
-      <c r="B287" s="13"/>
+      <c r="B287" s="14"/>
     </row>
     <row r="288">
-      <c r="B288" s="13"/>
+      <c r="B288" s="14"/>
     </row>
     <row r="289">
-      <c r="B289" s="13"/>
+      <c r="B289" s="14"/>
     </row>
     <row r="290">
-      <c r="B290" s="13"/>
+      <c r="B290" s="14"/>
     </row>
     <row r="291">
-      <c r="B291" s="13"/>
+      <c r="B291" s="14"/>
     </row>
     <row r="292">
-      <c r="B292" s="13"/>
+      <c r="B292" s="14"/>
     </row>
     <row r="293">
-      <c r="B293" s="13"/>
+      <c r="B293" s="14"/>
     </row>
     <row r="294">
-      <c r="B294" s="13"/>
+      <c r="B294" s="14"/>
     </row>
     <row r="295">
-      <c r="B295" s="13"/>
+      <c r="B295" s="14"/>
     </row>
     <row r="296">
-      <c r="B296" s="13"/>
+      <c r="B296" s="14"/>
     </row>
     <row r="297">
-      <c r="B297" s="13"/>
+      <c r="B297" s="14"/>
     </row>
     <row r="298">
-      <c r="B298" s="13"/>
+      <c r="B298" s="14"/>
     </row>
     <row r="299">
-      <c r="B299" s="13"/>
+      <c r="B299" s="14"/>
     </row>
     <row r="300">
-      <c r="B300" s="13"/>
+      <c r="B300" s="14"/>
     </row>
     <row r="301">
-      <c r="B301" s="13"/>
+      <c r="B301" s="14"/>
     </row>
     <row r="302">
-      <c r="B302" s="13"/>
+      <c r="B302" s="14"/>
     </row>
     <row r="303">
-      <c r="B303" s="13"/>
+      <c r="B303" s="14"/>
     </row>
     <row r="304">
-      <c r="B304" s="13"/>
+      <c r="B304" s="14"/>
     </row>
     <row r="305">
-      <c r="B305" s="13"/>
+      <c r="B305" s="14"/>
     </row>
     <row r="306">
-      <c r="B306" s="13"/>
+      <c r="B306" s="14"/>
     </row>
     <row r="307">
-      <c r="B307" s="13"/>
+      <c r="B307" s="14"/>
     </row>
     <row r="308">
-      <c r="B308" s="13"/>
+      <c r="B308" s="14"/>
     </row>
     <row r="309">
-      <c r="B309" s="13"/>
+      <c r="B309" s="14"/>
     </row>
     <row r="310">
-      <c r="B310" s="13"/>
+      <c r="B310" s="14"/>
     </row>
     <row r="311">
-      <c r="B311" s="13"/>
+      <c r="B311" s="14"/>
     </row>
     <row r="312">
-      <c r="B312" s="13"/>
+      <c r="B312" s="14"/>
     </row>
     <row r="313">
-      <c r="B313" s="13"/>
+      <c r="B313" s="14"/>
     </row>
     <row r="314">
-      <c r="B314" s="13"/>
+      <c r="B314" s="14"/>
     </row>
     <row r="315">
-      <c r="B315" s="13"/>
+      <c r="B315" s="14"/>
     </row>
     <row r="316">
-      <c r="B316" s="13"/>
+      <c r="B316" s="14"/>
     </row>
     <row r="317">
-      <c r="B317" s="13"/>
+      <c r="B317" s="14"/>
     </row>
     <row r="318">
-      <c r="B318" s="13"/>
+      <c r="B318" s="14"/>
     </row>
     <row r="319">
-      <c r="B319" s="13"/>
+      <c r="B319" s="14"/>
     </row>
     <row r="320">
-      <c r="B320" s="13"/>
+      <c r="B320" s="14"/>
     </row>
     <row r="321">
-      <c r="B321" s="13"/>
+      <c r="B321" s="14"/>
     </row>
     <row r="322">
-      <c r="B322" s="13"/>
+      <c r="B322" s="14"/>
     </row>
     <row r="323">
-      <c r="B323" s="13"/>
+      <c r="B323" s="14"/>
     </row>
     <row r="324">
-      <c r="B324" s="13"/>
+      <c r="B324" s="14"/>
     </row>
     <row r="325">
-      <c r="B325" s="13"/>
+      <c r="B325" s="14"/>
     </row>
     <row r="326">
-      <c r="B326" s="13"/>
+      <c r="B326" s="14"/>
     </row>
     <row r="327">
-      <c r="B327" s="13"/>
+      <c r="B327" s="14"/>
     </row>
     <row r="328">
-      <c r="B328" s="13"/>
+      <c r="B328" s="14"/>
     </row>
     <row r="329">
-      <c r="B329" s="13"/>
+      <c r="B329" s="14"/>
     </row>
     <row r="330">
-      <c r="B330" s="13"/>
+      <c r="B330" s="14"/>
     </row>
     <row r="331">
-      <c r="B331" s="13"/>
+      <c r="B331" s="14"/>
     </row>
     <row r="332">
-      <c r="B332" s="13"/>
+      <c r="B332" s="14"/>
     </row>
     <row r="333">
-      <c r="B333" s="13"/>
+      <c r="B333" s="14"/>
     </row>
     <row r="334">
-      <c r="B334" s="13"/>
+      <c r="B334" s="14"/>
     </row>
     <row r="335">
-      <c r="B335" s="13"/>
+      <c r="B335" s="14"/>
     </row>
     <row r="336">
-      <c r="B336" s="13"/>
+      <c r="B336" s="14"/>
     </row>
     <row r="337">
-      <c r="B337" s="13"/>
+      <c r="B337" s="14"/>
     </row>
     <row r="338">
-      <c r="B338" s="13"/>
+      <c r="B338" s="14"/>
     </row>
     <row r="339">
-      <c r="B339" s="13"/>
+      <c r="B339" s="14"/>
     </row>
     <row r="340">
-      <c r="B340" s="13"/>
+      <c r="B340" s="14"/>
     </row>
     <row r="341">
-      <c r="B341" s="13"/>
+      <c r="B341" s="14"/>
     </row>
     <row r="342">
-      <c r="B342" s="13"/>
+      <c r="B342" s="14"/>
     </row>
     <row r="343">
-      <c r="B343" s="13"/>
+      <c r="B343" s="14"/>
     </row>
     <row r="344">
-      <c r="B344" s="13"/>
+      <c r="B344" s="14"/>
     </row>
     <row r="345">
-      <c r="B345" s="13"/>
+      <c r="B345" s="14"/>
     </row>
     <row r="346">
-      <c r="B346" s="13"/>
+      <c r="B346" s="14"/>
     </row>
     <row r="347">
-      <c r="B347" s="13"/>
+      <c r="B347" s="14"/>
     </row>
     <row r="348">
-      <c r="B348" s="13"/>
+      <c r="B348" s="14"/>
     </row>
     <row r="349">
-      <c r="B349" s="13"/>
+      <c r="B349" s="14"/>
     </row>
     <row r="350">
-      <c r="B350" s="13"/>
+      <c r="B350" s="14"/>
     </row>
     <row r="351">
-      <c r="B351" s="13"/>
+      <c r="B351" s="14"/>
     </row>
     <row r="352">
-      <c r="B352" s="13"/>
+      <c r="B352" s="14"/>
     </row>
     <row r="353">
-      <c r="B353" s="13"/>
+      <c r="B353" s="14"/>
     </row>
     <row r="354">
-      <c r="B354" s="13"/>
+      <c r="B354" s="14"/>
     </row>
     <row r="355">
-      <c r="B355" s="13"/>
+      <c r="B355" s="14"/>
     </row>
     <row r="356">
-      <c r="B356" s="13"/>
+      <c r="B356" s="14"/>
     </row>
     <row r="357">
-      <c r="B357" s="13"/>
+      <c r="B357" s="14"/>
     </row>
     <row r="358">
-      <c r="B358" s="13"/>
+      <c r="B358" s="14"/>
     </row>
     <row r="359">
-      <c r="B359" s="13"/>
+      <c r="B359" s="14"/>
     </row>
     <row r="360">
-      <c r="B360" s="13"/>
+      <c r="B360" s="14"/>
     </row>
     <row r="361">
-      <c r="B361" s="13"/>
+      <c r="B361" s="14"/>
     </row>
     <row r="362">
-      <c r="B362" s="13"/>
+      <c r="B362" s="14"/>
     </row>
     <row r="363">
-      <c r="B363" s="13"/>
+      <c r="B363" s="14"/>
     </row>
     <row r="364">
-      <c r="B364" s="13"/>
+      <c r="B364" s="14"/>
     </row>
     <row r="365">
-      <c r="B365" s="13"/>
+      <c r="B365" s="14"/>
     </row>
     <row r="366">
-      <c r="B366" s="13"/>
+      <c r="B366" s="14"/>
     </row>
     <row r="367">
-      <c r="B367" s="13"/>
+      <c r="B367" s="14"/>
     </row>
     <row r="368">
-      <c r="B368" s="13"/>
+      <c r="B368" s="14"/>
     </row>
     <row r="369">
-      <c r="B369" s="13"/>
+      <c r="B369" s="14"/>
     </row>
     <row r="370">
-      <c r="B370" s="13"/>
+      <c r="B370" s="14"/>
     </row>
     <row r="371">
-      <c r="B371" s="13"/>
+      <c r="B371" s="14"/>
     </row>
     <row r="372">
-      <c r="B372" s="13"/>
+      <c r="B372" s="14"/>
     </row>
     <row r="373">
-      <c r="B373" s="13"/>
+      <c r="B373" s="14"/>
     </row>
     <row r="374">
-      <c r="B374" s="13"/>
+      <c r="B374" s="14"/>
     </row>
     <row r="375">
-      <c r="B375" s="13"/>
+      <c r="B375" s="14"/>
     </row>
     <row r="376">
-      <c r="B376" s="13"/>
+      <c r="B376" s="14"/>
     </row>
     <row r="377">
-      <c r="B377" s="13"/>
+      <c r="B377" s="14"/>
     </row>
     <row r="378">
-      <c r="B378" s="13"/>
+      <c r="B378" s="14"/>
     </row>
     <row r="379">
-      <c r="B379" s="13"/>
+      <c r="B379" s="14"/>
     </row>
     <row r="380">
-      <c r="B380" s="13"/>
+      <c r="B380" s="14"/>
     </row>
     <row r="381">
-      <c r="B381" s="13"/>
+      <c r="B381" s="14"/>
     </row>
     <row r="382">
-      <c r="B382" s="13"/>
+      <c r="B382" s="14"/>
     </row>
     <row r="383">
-      <c r="B383" s="13"/>
+      <c r="B383" s="14"/>
     </row>
     <row r="384">
-      <c r="B384" s="13"/>
+      <c r="B384" s="14"/>
     </row>
     <row r="385">
-      <c r="B385" s="13"/>
+      <c r="B385" s="14"/>
     </row>
     <row r="386">
-      <c r="B386" s="13"/>
+      <c r="B386" s="14"/>
     </row>
     <row r="387">
-      <c r="B387" s="13"/>
+      <c r="B387" s="14"/>
     </row>
     <row r="388">
-      <c r="B388" s="13"/>
+      <c r="B388" s="14"/>
     </row>
     <row r="389">
-      <c r="B389" s="13"/>
+      <c r="B389" s="14"/>
     </row>
     <row r="390">
-      <c r="B390" s="13"/>
+      <c r="B390" s="14"/>
     </row>
     <row r="391">
-      <c r="B391" s="13"/>
+      <c r="B391" s="14"/>
     </row>
     <row r="392">
-      <c r="B392" s="13"/>
+      <c r="B392" s="14"/>
     </row>
     <row r="393">
-      <c r="B393" s="13"/>
+      <c r="B393" s="14"/>
     </row>
     <row r="394">
-      <c r="B394" s="13"/>
+      <c r="B394" s="14"/>
     </row>
     <row r="395">
-      <c r="B395" s="13"/>
+      <c r="B395" s="14"/>
     </row>
     <row r="396">
-      <c r="B396" s="13"/>
+      <c r="B396" s="14"/>
     </row>
     <row r="397">
-      <c r="B397" s="13"/>
+      <c r="B397" s="14"/>
     </row>
     <row r="398">
-      <c r="B398" s="13"/>
+      <c r="B398" s="14"/>
     </row>
     <row r="399">
-      <c r="B399" s="13"/>
+      <c r="B399" s="14"/>
     </row>
     <row r="400">
-      <c r="B400" s="13"/>
+      <c r="B400" s="14"/>
     </row>
     <row r="401">
-      <c r="B401" s="13"/>
+      <c r="B401" s="14"/>
     </row>
     <row r="402">
-      <c r="B402" s="13"/>
+      <c r="B402" s="14"/>
     </row>
     <row r="403">
-      <c r="B403" s="13"/>
+      <c r="B403" s="14"/>
     </row>
     <row r="404">
-      <c r="B404" s="13"/>
+      <c r="B404" s="14"/>
     </row>
     <row r="405">
-      <c r="B405" s="13"/>
+      <c r="B405" s="14"/>
     </row>
     <row r="406">
-      <c r="B406" s="13"/>
+      <c r="B406" s="14"/>
     </row>
     <row r="407">
-      <c r="B407" s="13"/>
+      <c r="B407" s="14"/>
     </row>
     <row r="408">
-      <c r="B408" s="13"/>
+      <c r="B408" s="14"/>
     </row>
     <row r="409">
-      <c r="B409" s="13"/>
+      <c r="B409" s="14"/>
     </row>
     <row r="410">
-      <c r="B410" s="13"/>
+      <c r="B410" s="14"/>
     </row>
     <row r="411">
-      <c r="B411" s="13"/>
+      <c r="B411" s="14"/>
     </row>
     <row r="412">
-      <c r="B412" s="13"/>
+      <c r="B412" s="14"/>
     </row>
     <row r="413">
-      <c r="B413" s="13"/>
+      <c r="B413" s="14"/>
     </row>
     <row r="414">
-      <c r="B414" s="13"/>
+      <c r="B414" s="14"/>
     </row>
     <row r="415">
-      <c r="B415" s="13"/>
+      <c r="B415" s="14"/>
     </row>
     <row r="416">
-      <c r="B416" s="13"/>
+      <c r="B416" s="14"/>
     </row>
     <row r="417">
-      <c r="B417" s="13"/>
+      <c r="B417" s="14"/>
     </row>
     <row r="418">
-      <c r="B418" s="13"/>
+      <c r="B418" s="14"/>
     </row>
     <row r="419">
-      <c r="B419" s="13"/>
+      <c r="B419" s="14"/>
     </row>
     <row r="420">
-      <c r="B420" s="13"/>
+      <c r="B420" s="14"/>
     </row>
     <row r="421">
-      <c r="B421" s="13"/>
+      <c r="B421" s="14"/>
     </row>
     <row r="422">
-      <c r="B422" s="13"/>
+      <c r="B422" s="14"/>
     </row>
     <row r="423">
-      <c r="B423" s="13"/>
+      <c r="B423" s="14"/>
     </row>
     <row r="424">
-      <c r="B424" s="13"/>
+      <c r="B424" s="14"/>
     </row>
     <row r="425">
-      <c r="B425" s="13"/>
+      <c r="B425" s="14"/>
     </row>
     <row r="426">
-      <c r="B426" s="13"/>
+      <c r="B426" s="14"/>
     </row>
     <row r="427">
-      <c r="B427" s="13"/>
+      <c r="B427" s="14"/>
     </row>
     <row r="428">
-      <c r="B428" s="13"/>
+      <c r="B428" s="14"/>
     </row>
     <row r="429">
-      <c r="B429" s="13"/>
+      <c r="B429" s="14"/>
     </row>
     <row r="430">
-      <c r="B430" s="13"/>
+      <c r="B430" s="14"/>
     </row>
     <row r="431">
-      <c r="B431" s="13"/>
+      <c r="B431" s="14"/>
     </row>
     <row r="432">
-      <c r="B432" s="13"/>
+      <c r="B432" s="14"/>
     </row>
     <row r="433">
-      <c r="B433" s="13"/>
+      <c r="B433" s="14"/>
     </row>
     <row r="434">
-      <c r="B434" s="13"/>
+      <c r="B434" s="14"/>
     </row>
     <row r="435">
-      <c r="B435" s="13"/>
+      <c r="B435" s="14"/>
     </row>
     <row r="436">
-      <c r="B436" s="13"/>
+      <c r="B436" s="14"/>
     </row>
     <row r="437">
-      <c r="B437" s="13"/>
+      <c r="B437" s="14"/>
     </row>
     <row r="438">
-      <c r="B438" s="13"/>
+      <c r="B438" s="14"/>
     </row>
     <row r="439">
-      <c r="B439" s="13"/>
+      <c r="B439" s="14"/>
     </row>
     <row r="440">
-      <c r="B440" s="13"/>
+      <c r="B440" s="14"/>
     </row>
     <row r="441">
-      <c r="B441" s="13"/>
+      <c r="B441" s="14"/>
     </row>
     <row r="442">
-      <c r="B442" s="13"/>
+      <c r="B442" s="14"/>
     </row>
     <row r="443">
-      <c r="B443" s="13"/>
+      <c r="B443" s="14"/>
     </row>
     <row r="444">
-      <c r="B444" s="13"/>
+      <c r="B444" s="14"/>
     </row>
     <row r="445">
-      <c r="B445" s="13"/>
+      <c r="B445" s="14"/>
     </row>
     <row r="446">
-      <c r="B446" s="13"/>
+      <c r="B446" s="14"/>
     </row>
     <row r="447">
-      <c r="B447" s="13"/>
+      <c r="B447" s="14"/>
     </row>
     <row r="448">
-      <c r="B448" s="13"/>
+      <c r="B448" s="14"/>
     </row>
     <row r="449">
-      <c r="B449" s="13"/>
+      <c r="B449" s="14"/>
     </row>
     <row r="450">
-      <c r="B450" s="13"/>
+      <c r="B450" s="14"/>
     </row>
     <row r="451">
-      <c r="B451" s="13"/>
+      <c r="B451" s="14"/>
     </row>
     <row r="452">
-      <c r="B452" s="13"/>
+      <c r="B452" s="14"/>
     </row>
     <row r="453">
-      <c r="B453" s="13"/>
+      <c r="B453" s="14"/>
     </row>
     <row r="454">
-      <c r="B454" s="13"/>
+      <c r="B454" s="14"/>
     </row>
     <row r="455">
-      <c r="B455" s="13"/>
+      <c r="B455" s="14"/>
     </row>
     <row r="456">
-      <c r="B456" s="13"/>
+      <c r="B456" s="14"/>
     </row>
     <row r="457">
-      <c r="B457" s="13"/>
+      <c r="B457" s="14"/>
     </row>
     <row r="458">
-      <c r="B458" s="13"/>
+      <c r="B458" s="14"/>
     </row>
     <row r="459">
-      <c r="B459" s="13"/>
+      <c r="B459" s="14"/>
     </row>
     <row r="460">
-      <c r="B460" s="13"/>
+      <c r="B460" s="14"/>
     </row>
     <row r="461">
-      <c r="B461" s="13"/>
+      <c r="B461" s="14"/>
     </row>
     <row r="462">
-      <c r="B462" s="13"/>
+      <c r="B462" s="14"/>
     </row>
     <row r="463">
-      <c r="B463" s="13"/>
+      <c r="B463" s="14"/>
     </row>
     <row r="464">
-      <c r="B464" s="13"/>
+      <c r="B464" s="14"/>
     </row>
     <row r="465">
-      <c r="B465" s="13"/>
+      <c r="B465" s="14"/>
     </row>
     <row r="466">
-      <c r="B466" s="13"/>
+      <c r="B466" s="14"/>
     </row>
     <row r="467">
-      <c r="B467" s="13"/>
+      <c r="B467" s="14"/>
     </row>
     <row r="468">
-      <c r="B468" s="13"/>
+      <c r="B468" s="14"/>
     </row>
     <row r="469">
-      <c r="B469" s="13"/>
+      <c r="B469" s="14"/>
     </row>
     <row r="470">
-      <c r="B470" s="13"/>
+      <c r="B470" s="14"/>
     </row>
     <row r="471">
-      <c r="B471" s="13"/>
+      <c r="B471" s="14"/>
     </row>
     <row r="472">
-      <c r="B472" s="13"/>
+      <c r="B472" s="14"/>
     </row>
     <row r="473">
-      <c r="B473" s="13"/>
+      <c r="B473" s="14"/>
     </row>
     <row r="474">
-      <c r="B474" s="13"/>
+      <c r="B474" s="14"/>
     </row>
     <row r="475">
-      <c r="B475" s="13"/>
+      <c r="B475" s="14"/>
     </row>
     <row r="476">
-      <c r="B476" s="13"/>
+      <c r="B476" s="14"/>
     </row>
     <row r="477">
-      <c r="B477" s="13"/>
+      <c r="B477" s="14"/>
     </row>
     <row r="478">
-      <c r="B478" s="13"/>
+      <c r="B478" s="14"/>
     </row>
     <row r="479">
-      <c r="B479" s="13"/>
+      <c r="B479" s="14"/>
     </row>
     <row r="480">
-      <c r="B480" s="13"/>
+      <c r="B480" s="14"/>
     </row>
     <row r="481">
-      <c r="B481" s="13"/>
+      <c r="B481" s="14"/>
     </row>
     <row r="482">
-      <c r="B482" s="13"/>
+      <c r="B482" s="14"/>
     </row>
     <row r="483">
-      <c r="B483" s="13"/>
+      <c r="B483" s="14"/>
     </row>
     <row r="484">
-      <c r="B484" s="13"/>
+      <c r="B484" s="14"/>
     </row>
     <row r="485">
-      <c r="B485" s="13"/>
+      <c r="B485" s="14"/>
     </row>
     <row r="486">
-      <c r="B486" s="13"/>
+      <c r="B486" s="14"/>
     </row>
     <row r="487">
-      <c r="B487" s="13"/>
+      <c r="B487" s="14"/>
     </row>
     <row r="488">
-      <c r="B488" s="13"/>
+      <c r="B488" s="14"/>
     </row>
     <row r="489">
-      <c r="B489" s="13"/>
+      <c r="B489" s="14"/>
     </row>
     <row r="490">
-      <c r="B490" s="13"/>
+      <c r="B490" s="14"/>
     </row>
     <row r="491">
-      <c r="B491" s="13"/>
+      <c r="B491" s="14"/>
     </row>
     <row r="492">
-      <c r="B492" s="13"/>
+      <c r="B492" s="14"/>
     </row>
     <row r="493">
-      <c r="B493" s="13"/>
+      <c r="B493" s="14"/>
     </row>
     <row r="494">
-      <c r="B494" s="13"/>
+      <c r="B494" s="14"/>
     </row>
     <row r="495">
-      <c r="B495" s="13"/>
+      <c r="B495" s="14"/>
     </row>
     <row r="496">
-      <c r="B496" s="13"/>
+      <c r="B496" s="14"/>
     </row>
     <row r="497">
-      <c r="B497" s="13"/>
+      <c r="B497" s="14"/>
     </row>
     <row r="498">
-      <c r="B498" s="13"/>
+      <c r="B498" s="14"/>
     </row>
     <row r="499">
-      <c r="B499" s="13"/>
+      <c r="B499" s="14"/>
     </row>
     <row r="500">
-      <c r="B500" s="13"/>
+      <c r="B500" s="14"/>
     </row>
     <row r="501">
-      <c r="B501" s="13"/>
+      <c r="B501" s="14"/>
     </row>
     <row r="502">
-      <c r="B502" s="13"/>
+      <c r="B502" s="14"/>
     </row>
     <row r="503">
-      <c r="B503" s="13"/>
+      <c r="B503" s="14"/>
     </row>
     <row r="504">
-      <c r="B504" s="13"/>
+      <c r="B504" s="14"/>
     </row>
     <row r="505">
-      <c r="B505" s="13"/>
+      <c r="B505" s="14"/>
     </row>
     <row r="506">
-      <c r="B506" s="13"/>
+      <c r="B506" s="14"/>
     </row>
     <row r="507">
-      <c r="B507" s="13"/>
+      <c r="B507" s="14"/>
     </row>
     <row r="508">
-      <c r="B508" s="13"/>
+      <c r="B508" s="14"/>
     </row>
     <row r="509">
-      <c r="B509" s="13"/>
+      <c r="B509" s="14"/>
     </row>
     <row r="510">
-      <c r="B510" s="13"/>
+      <c r="B510" s="14"/>
     </row>
     <row r="511">
-      <c r="B511" s="13"/>
+      <c r="B511" s="14"/>
     </row>
     <row r="512">
-      <c r="B512" s="13"/>
+      <c r="B512" s="14"/>
     </row>
     <row r="513">
-      <c r="B513" s="13"/>
+      <c r="B513" s="14"/>
     </row>
     <row r="514">
-      <c r="B514" s="13"/>
+      <c r="B514" s="14"/>
     </row>
     <row r="515">
-      <c r="B515" s="13"/>
+      <c r="B515" s="14"/>
     </row>
     <row r="516">
-      <c r="B516" s="13"/>
+      <c r="B516" s="14"/>
     </row>
     <row r="517">
-      <c r="B517" s="13"/>
+      <c r="B517" s="14"/>
     </row>
     <row r="518">
-      <c r="B518" s="13"/>
+      <c r="B518" s="14"/>
     </row>
     <row r="519">
-      <c r="B519" s="13"/>
+      <c r="B519" s="14"/>
     </row>
     <row r="520">
-      <c r="B520" s="13"/>
+      <c r="B520" s="14"/>
     </row>
     <row r="521">
-      <c r="B521" s="13"/>
+      <c r="B521" s="14"/>
     </row>
     <row r="522">
-      <c r="B522" s="13"/>
+      <c r="B522" s="14"/>
     </row>
     <row r="523">
-      <c r="B523" s="13"/>
+      <c r="B523" s="14"/>
     </row>
     <row r="524">
-      <c r="B524" s="13"/>
+      <c r="B524" s="14"/>
     </row>
     <row r="525">
-      <c r="B525" s="13"/>
+      <c r="B525" s="14"/>
     </row>
     <row r="526">
-      <c r="B526" s="13"/>
+      <c r="B526" s="14"/>
     </row>
     <row r="527">
-      <c r="B527" s="13"/>
+      <c r="B527" s="14"/>
     </row>
     <row r="528">
-      <c r="B528" s="13"/>
+      <c r="B528" s="14"/>
     </row>
     <row r="529">
-      <c r="B529" s="13"/>
+      <c r="B529" s="14"/>
     </row>
     <row r="530">
-      <c r="B530" s="13"/>
+      <c r="B530" s="14"/>
     </row>
     <row r="531">
-      <c r="B531" s="13"/>
+      <c r="B531" s="14"/>
     </row>
     <row r="532">
-      <c r="B532" s="13"/>
+      <c r="B532" s="14"/>
     </row>
     <row r="533">
-      <c r="B533" s="13"/>
+      <c r="B533" s="14"/>
     </row>
     <row r="534">
-      <c r="B534" s="13"/>
+      <c r="B534" s="14"/>
     </row>
     <row r="535">
-      <c r="B535" s="13"/>
+      <c r="B535" s="14"/>
     </row>
     <row r="536">
-      <c r="B536" s="13"/>
+      <c r="B536" s="14"/>
     </row>
     <row r="537">
-      <c r="B537" s="13"/>
+      <c r="B537" s="14"/>
     </row>
     <row r="538">
-      <c r="B538" s="13"/>
+      <c r="B538" s="14"/>
     </row>
     <row r="539">
-      <c r="B539" s="13"/>
+      <c r="B539" s="14"/>
     </row>
     <row r="540">
-      <c r="B540" s="13"/>
+      <c r="B540" s="14"/>
     </row>
     <row r="541">
-      <c r="B541" s="13"/>
+      <c r="B541" s="14"/>
     </row>
     <row r="542">
-      <c r="B542" s="13"/>
+      <c r="B542" s="14"/>
     </row>
     <row r="543">
-      <c r="B543" s="13"/>
+      <c r="B543" s="14"/>
     </row>
     <row r="544">
-      <c r="B544" s="13"/>
+      <c r="B544" s="14"/>
     </row>
     <row r="545">
-      <c r="B545" s="13"/>
+      <c r="B545" s="14"/>
     </row>
     <row r="546">
-      <c r="B546" s="13"/>
+      <c r="B546" s="14"/>
     </row>
     <row r="547">
-      <c r="B547" s="13"/>
+      <c r="B547" s="14"/>
     </row>
     <row r="548">
-      <c r="B548" s="13"/>
+      <c r="B548" s="14"/>
     </row>
     <row r="549">
-      <c r="B549" s="13"/>
+      <c r="B549" s="14"/>
     </row>
     <row r="550">
-      <c r="B550" s="13"/>
+      <c r="B550" s="14"/>
     </row>
     <row r="551">
-      <c r="B551" s="13"/>
+      <c r="B551" s="14"/>
     </row>
     <row r="552">
-      <c r="B552" s="13"/>
+      <c r="B552" s="14"/>
     </row>
     <row r="553">
-      <c r="B553" s="13"/>
+      <c r="B553" s="14"/>
     </row>
     <row r="554">
-      <c r="B554" s="13"/>
+      <c r="B554" s="14"/>
     </row>
     <row r="555">
-      <c r="B555" s="13"/>
+      <c r="B555" s="14"/>
     </row>
     <row r="556">
-      <c r="B556" s="13"/>
+      <c r="B556" s="14"/>
     </row>
     <row r="557">
-      <c r="B557" s="13"/>
+      <c r="B557" s="14"/>
     </row>
     <row r="558">
-      <c r="B558" s="13"/>
+      <c r="B558" s="14"/>
     </row>
     <row r="559">
-      <c r="B559" s="13"/>
+      <c r="B559" s="14"/>
     </row>
     <row r="560">
-      <c r="B560" s="13"/>
+      <c r="B560" s="14"/>
     </row>
     <row r="561">
-      <c r="B561" s="13"/>
+      <c r="B561" s="14"/>
     </row>
     <row r="562">
-      <c r="B562" s="13"/>
+      <c r="B562" s="14"/>
     </row>
     <row r="563">
-      <c r="B563" s="13"/>
+      <c r="B563" s="14"/>
     </row>
     <row r="564">
-      <c r="B564" s="13"/>
+      <c r="B564" s="14"/>
     </row>
     <row r="565">
-      <c r="B565" s="13"/>
+      <c r="B565" s="14"/>
     </row>
     <row r="566">
-      <c r="B566" s="13"/>
+      <c r="B566" s="14"/>
     </row>
     <row r="567">
-      <c r="B567" s="13"/>
+      <c r="B567" s="14"/>
     </row>
     <row r="568">
-      <c r="B568" s="13"/>
+      <c r="B568" s="14"/>
     </row>
     <row r="569">
-      <c r="B569" s="13"/>
+      <c r="B569" s="14"/>
     </row>
     <row r="570">
-      <c r="B570" s="13"/>
+      <c r="B570" s="14"/>
     </row>
     <row r="571">
-      <c r="B571" s="13"/>
+      <c r="B571" s="14"/>
     </row>
     <row r="572">
-      <c r="B572" s="13"/>
+      <c r="B572" s="14"/>
     </row>
     <row r="573">
-      <c r="B573" s="13"/>
+      <c r="B573" s="14"/>
     </row>
     <row r="574">
-      <c r="B574" s="13"/>
+      <c r="B574" s="14"/>
     </row>
     <row r="575">
-      <c r="B575" s="13"/>
+      <c r="B575" s="14"/>
     </row>
     <row r="576">
-      <c r="B576" s="13"/>
+      <c r="B576" s="14"/>
     </row>
     <row r="577">
-      <c r="B577" s="13"/>
+      <c r="B577" s="14"/>
     </row>
     <row r="578">
-      <c r="B578" s="13"/>
+      <c r="B578" s="14"/>
     </row>
     <row r="579">
-      <c r="B579" s="13"/>
+      <c r="B579" s="14"/>
     </row>
     <row r="580">
-      <c r="B580" s="13"/>
+      <c r="B580" s="14"/>
     </row>
     <row r="581">
-      <c r="B581" s="13"/>
+      <c r="B581" s="14"/>
     </row>
     <row r="582">
-      <c r="B582" s="13"/>
+      <c r="B582" s="14"/>
     </row>
     <row r="583">
-      <c r="B583" s="13"/>
+      <c r="B583" s="14"/>
     </row>
     <row r="584">
-      <c r="B584" s="13"/>
+      <c r="B584" s="14"/>
     </row>
     <row r="585">
-      <c r="B585" s="13"/>
+      <c r="B585" s="14"/>
     </row>
     <row r="586">
-      <c r="B586" s="13"/>
+      <c r="B586" s="14"/>
     </row>
     <row r="587">
-      <c r="B587" s="13"/>
+      <c r="B587" s="14"/>
     </row>
     <row r="588">
-      <c r="B588" s="13"/>
+      <c r="B588" s="14"/>
     </row>
     <row r="589">
-      <c r="B589" s="13"/>
+      <c r="B589" s="14"/>
     </row>
     <row r="590">
-      <c r="B590" s="13"/>
+      <c r="B590" s="14"/>
     </row>
     <row r="591">
-      <c r="B591" s="13"/>
+      <c r="B591" s="14"/>
     </row>
     <row r="592">
-      <c r="B592" s="13"/>
+      <c r="B592" s="14"/>
     </row>
     <row r="593">
-      <c r="B593" s="13"/>
+      <c r="B593" s="14"/>
     </row>
     <row r="594">
-      <c r="B594" s="13"/>
+      <c r="B594" s="14"/>
     </row>
     <row r="595">
-      <c r="B595" s="13"/>
+      <c r="B595" s="14"/>
     </row>
     <row r="596">
-      <c r="B596" s="13"/>
+      <c r="B596" s="14"/>
     </row>
     <row r="597">
-      <c r="B597" s="13"/>
+      <c r="B597" s="14"/>
     </row>
     <row r="598">
-      <c r="B598" s="13"/>
+      <c r="B598" s="14"/>
     </row>
     <row r="599">
-      <c r="B599" s="13"/>
+      <c r="B599" s="14"/>
     </row>
     <row r="600">
-      <c r="B600" s="13"/>
+      <c r="B600" s="14"/>
     </row>
     <row r="601">
-      <c r="B601" s="13"/>
+      <c r="B601" s="14"/>
     </row>
     <row r="602">
-      <c r="B602" s="13"/>
+      <c r="B602" s="14"/>
     </row>
     <row r="603">
-      <c r="B603" s="13"/>
+      <c r="B603" s="14"/>
     </row>
     <row r="604">
-      <c r="B604" s="13"/>
+      <c r="B604" s="14"/>
     </row>
     <row r="605">
-      <c r="B605" s="13"/>
+      <c r="B605" s="14"/>
     </row>
     <row r="606">
-      <c r="B606" s="13"/>
+      <c r="B606" s="14"/>
     </row>
     <row r="607">
-      <c r="B607" s="13"/>
+      <c r="B607" s="14"/>
     </row>
     <row r="608">
-      <c r="B608" s="13"/>
+      <c r="B608" s="14"/>
     </row>
     <row r="609">
-      <c r="B609" s="13"/>
+      <c r="B609" s="14"/>
     </row>
     <row r="610">
-      <c r="B610" s="13"/>
+      <c r="B610" s="14"/>
     </row>
     <row r="611">
-      <c r="B611" s="13"/>
+      <c r="B611" s="14"/>
     </row>
     <row r="612">
-      <c r="B612" s="13"/>
+      <c r="B612" s="14"/>
     </row>
     <row r="613">
-      <c r="B613" s="13"/>
+      <c r="B613" s="14"/>
     </row>
     <row r="614">
-      <c r="B614" s="13"/>
+      <c r="B614" s="14"/>
     </row>
     <row r="615">
-      <c r="B615" s="13"/>
+      <c r="B615" s="14"/>
     </row>
     <row r="616">
-      <c r="B616" s="13"/>
+      <c r="B616" s="14"/>
     </row>
     <row r="617">
-      <c r="B617" s="13"/>
+      <c r="B617" s="14"/>
     </row>
     <row r="618">
-      <c r="B618" s="13"/>
+      <c r="B618" s="14"/>
     </row>
     <row r="619">
-      <c r="B619" s="13"/>
+      <c r="B619" s="14"/>
     </row>
     <row r="620">
-      <c r="B620" s="13"/>
+      <c r="B620" s="14"/>
     </row>
     <row r="621">
-      <c r="B621" s="13"/>
+      <c r="B621" s="14"/>
     </row>
     <row r="622">
-      <c r="B622" s="13"/>
+      <c r="B622" s="14"/>
     </row>
     <row r="623">
-      <c r="B623" s="13"/>
+      <c r="B623" s="14"/>
     </row>
     <row r="624">
-      <c r="B624" s="13"/>
+      <c r="B624" s="14"/>
     </row>
     <row r="625">
-      <c r="B625" s="13"/>
+      <c r="B625" s="14"/>
     </row>
     <row r="626">
-      <c r="B626" s="13"/>
+      <c r="B626" s="14"/>
     </row>
     <row r="627">
-      <c r="B627" s="13"/>
+      <c r="B627" s="14"/>
     </row>
     <row r="628">
-      <c r="B628" s="13"/>
+      <c r="B628" s="14"/>
     </row>
     <row r="629">
-      <c r="B629" s="13"/>
+      <c r="B629" s="14"/>
     </row>
     <row r="630">
-      <c r="B630" s="13"/>
+      <c r="B630" s="14"/>
     </row>
     <row r="631">
-      <c r="B631" s="13"/>
+      <c r="B631" s="14"/>
     </row>
     <row r="632">
-      <c r="B632" s="13"/>
+      <c r="B632" s="14"/>
     </row>
     <row r="633">
-      <c r="B633" s="13"/>
+      <c r="B633" s="14"/>
     </row>
     <row r="634">
-      <c r="B634" s="13"/>
+      <c r="B634" s="14"/>
     </row>
     <row r="635">
-      <c r="B635" s="13"/>
+      <c r="B635" s="14"/>
     </row>
     <row r="636">
-      <c r="B636" s="13"/>
+      <c r="B636" s="14"/>
     </row>
     <row r="637">
-      <c r="B637" s="13"/>
+      <c r="B637" s="14"/>
     </row>
     <row r="638">
-      <c r="B638" s="13"/>
+      <c r="B638" s="14"/>
     </row>
     <row r="639">
-      <c r="B639" s="13"/>
+      <c r="B639" s="14"/>
     </row>
     <row r="640">
-      <c r="B640" s="13"/>
+      <c r="B640" s="14"/>
     </row>
     <row r="641">
-      <c r="B641" s="13"/>
+      <c r="B641" s="14"/>
     </row>
     <row r="642">
-      <c r="B642" s="13"/>
+      <c r="B642" s="14"/>
     </row>
     <row r="643">
-      <c r="B643" s="13"/>
+      <c r="B643" s="14"/>
     </row>
     <row r="644">
-      <c r="B644" s="13"/>
+      <c r="B644" s="14"/>
     </row>
     <row r="645">
-      <c r="B645" s="13"/>
+      <c r="B645" s="14"/>
     </row>
     <row r="646">
-      <c r="B646" s="13"/>
+      <c r="B646" s="14"/>
     </row>
     <row r="647">
-      <c r="B647" s="13"/>
+      <c r="B647" s="14"/>
     </row>
     <row r="648">
-      <c r="B648" s="13"/>
+      <c r="B648" s="14"/>
     </row>
     <row r="649">
-      <c r="B649" s="13"/>
+      <c r="B649" s="14"/>
     </row>
     <row r="650">
-      <c r="B650" s="13"/>
+      <c r="B650" s="14"/>
     </row>
     <row r="651">
-      <c r="B651" s="13"/>
+      <c r="B651" s="14"/>
     </row>
     <row r="652">
-      <c r="B652" s="13"/>
+      <c r="B652" s="14"/>
     </row>
     <row r="653">
-      <c r="B653" s="13"/>
+      <c r="B653" s="14"/>
     </row>
     <row r="654">
-      <c r="B654" s="13"/>
+      <c r="B654" s="14"/>
     </row>
     <row r="655">
-      <c r="B655" s="13"/>
+      <c r="B655" s="14"/>
     </row>
     <row r="656">
-      <c r="B656" s="13"/>
+      <c r="B656" s="14"/>
     </row>
     <row r="657">
-      <c r="B657" s="13"/>
+      <c r="B657" s="14"/>
     </row>
     <row r="658">
-      <c r="B658" s="13"/>
+      <c r="B658" s="14"/>
     </row>
     <row r="659">
-      <c r="B659" s="13"/>
+      <c r="B659" s="14"/>
     </row>
     <row r="660">
-      <c r="B660" s="13"/>
+      <c r="B660" s="14"/>
     </row>
     <row r="661">
-      <c r="B661" s="13"/>
+      <c r="B661" s="14"/>
     </row>
     <row r="662">
-      <c r="B662" s="13"/>
+      <c r="B662" s="14"/>
     </row>
     <row r="663">
-      <c r="B663" s="13"/>
+      <c r="B663" s="14"/>
     </row>
     <row r="664">
-      <c r="B664" s="13"/>
+      <c r="B664" s="14"/>
     </row>
     <row r="665">
-      <c r="B665" s="13"/>
+      <c r="B665" s="14"/>
     </row>
     <row r="666">
-      <c r="B666" s="13"/>
+      <c r="B666" s="14"/>
     </row>
     <row r="667">
-      <c r="B667" s="13"/>
+      <c r="B667" s="14"/>
     </row>
     <row r="668">
-      <c r="B668" s="13"/>
+      <c r="B668" s="14"/>
     </row>
     <row r="669">
-      <c r="B669" s="13"/>
+      <c r="B669" s="14"/>
     </row>
     <row r="670">
-      <c r="B670" s="13"/>
+      <c r="B670" s="14"/>
     </row>
     <row r="671">
-      <c r="B671" s="13"/>
+      <c r="B671" s="14"/>
     </row>
     <row r="672">
-      <c r="B672" s="13"/>
+      <c r="B672" s="14"/>
     </row>
     <row r="673">
-      <c r="B673" s="13"/>
+      <c r="B673" s="14"/>
     </row>
     <row r="674">
-      <c r="B674" s="13"/>
+      <c r="B674" s="14"/>
     </row>
     <row r="675">
-      <c r="B675" s="13"/>
+      <c r="B675" s="14"/>
     </row>
     <row r="676">
-      <c r="B676" s="13"/>
+      <c r="B676" s="14"/>
     </row>
     <row r="677">
-      <c r="B677" s="13"/>
+      <c r="B677" s="14"/>
     </row>
     <row r="678">
-      <c r="B678" s="13"/>
+      <c r="B678" s="14"/>
     </row>
     <row r="679">
-      <c r="B679" s="13"/>
+      <c r="B679" s="14"/>
     </row>
     <row r="680">
-      <c r="B680" s="13"/>
+      <c r="B680" s="14"/>
     </row>
     <row r="681">
-      <c r="B681" s="13"/>
+      <c r="B681" s="14"/>
     </row>
     <row r="682">
-      <c r="B682" s="13"/>
+      <c r="B682" s="14"/>
     </row>
     <row r="683">
-      <c r="B683" s="13"/>
+      <c r="B683" s="14"/>
     </row>
     <row r="684">
-      <c r="B684" s="13"/>
+      <c r="B684" s="14"/>
     </row>
     <row r="685">
-      <c r="B685" s="13"/>
+      <c r="B685" s="14"/>
     </row>
     <row r="686">
-      <c r="B686" s="13"/>
+      <c r="B686" s="14"/>
     </row>
     <row r="687">
-      <c r="B687" s="13"/>
+      <c r="B687" s="14"/>
     </row>
     <row r="688">
-      <c r="B688" s="13"/>
+      <c r="B688" s="14"/>
     </row>
     <row r="689">
-      <c r="B689" s="13"/>
+      <c r="B689" s="14"/>
     </row>
     <row r="690">
-      <c r="B690" s="13"/>
+      <c r="B690" s="14"/>
     </row>
     <row r="691">
-      <c r="B691" s="13"/>
+      <c r="B691" s="14"/>
     </row>
     <row r="692">
-      <c r="B692" s="13"/>
+      <c r="B692" s="14"/>
     </row>
     <row r="693">
-      <c r="B693" s="13"/>
+      <c r="B693" s="14"/>
     </row>
     <row r="694">
-      <c r="B694" s="13"/>
+      <c r="B694" s="14"/>
     </row>
     <row r="695">
-      <c r="B695" s="13"/>
+      <c r="B695" s="14"/>
     </row>
     <row r="696">
-      <c r="B696" s="13"/>
+      <c r="B696" s="14"/>
     </row>
     <row r="697">
-      <c r="B697" s="13"/>
+      <c r="B697" s="14"/>
     </row>
     <row r="698">
-      <c r="B698" s="13"/>
+      <c r="B698" s="14"/>
     </row>
     <row r="699">
-      <c r="B699" s="13"/>
+      <c r="B699" s="14"/>
     </row>
     <row r="700">
-      <c r="B700" s="13"/>
+      <c r="B700" s="14"/>
     </row>
     <row r="701">
-      <c r="B701" s="13"/>
+      <c r="B701" s="14"/>
     </row>
     <row r="702">
-      <c r="B702" s="13"/>
+      <c r="B702" s="14"/>
     </row>
     <row r="703">
-      <c r="B703" s="13"/>
+      <c r="B703" s="14"/>
     </row>
     <row r="704">
-      <c r="B704" s="13"/>
+      <c r="B704" s="14"/>
     </row>
     <row r="705">
-      <c r="B705" s="13"/>
+      <c r="B705" s="14"/>
     </row>
     <row r="706">
-      <c r="B706" s="13"/>
+      <c r="B706" s="14"/>
     </row>
     <row r="707">
-      <c r="B707" s="13"/>
+      <c r="B707" s="14"/>
     </row>
     <row r="708">
-      <c r="B708" s="13"/>
+      <c r="B708" s="14"/>
     </row>
     <row r="709">
-      <c r="B709" s="13"/>
+      <c r="B709" s="14"/>
     </row>
     <row r="710">
-      <c r="B710" s="13"/>
+      <c r="B710" s="14"/>
     </row>
     <row r="711">
-      <c r="B711" s="13"/>
+      <c r="B711" s="14"/>
     </row>
     <row r="712">
-      <c r="B712" s="13"/>
+      <c r="B712" s="14"/>
     </row>
     <row r="713">
-      <c r="B713" s="13"/>
+      <c r="B713" s="14"/>
     </row>
     <row r="714">
-      <c r="B714" s="13"/>
+      <c r="B714" s="14"/>
     </row>
     <row r="715">
-      <c r="B715" s="13"/>
+      <c r="B715" s="14"/>
     </row>
     <row r="716">
-      <c r="B716" s="13"/>
+      <c r="B716" s="14"/>
     </row>
     <row r="717">
-      <c r="B717" s="13"/>
+      <c r="B717" s="14"/>
     </row>
     <row r="718">
-      <c r="B718" s="13"/>
+      <c r="B718" s="14"/>
     </row>
     <row r="719">
-      <c r="B719" s="13"/>
+      <c r="B719" s="14"/>
     </row>
     <row r="720">
-      <c r="B720" s="13"/>
+      <c r="B720" s="14"/>
     </row>
     <row r="721">
-      <c r="B721" s="13"/>
+      <c r="B721" s="14"/>
     </row>
     <row r="722">
-      <c r="B722" s="13"/>
+      <c r="B722" s="14"/>
     </row>
     <row r="723">
-      <c r="B723" s="13"/>
+      <c r="B723" s="14"/>
     </row>
     <row r="724">
-      <c r="B724" s="13"/>
+      <c r="B724" s="14"/>
     </row>
     <row r="725">
-      <c r="B725" s="13"/>
+      <c r="B725" s="14"/>
     </row>
     <row r="726">
-      <c r="B726" s="13"/>
+      <c r="B726" s="14"/>
     </row>
     <row r="727">
-      <c r="B727" s="13"/>
+      <c r="B727" s="14"/>
     </row>
     <row r="728">
-      <c r="B728" s="13"/>
+      <c r="B728" s="14"/>
     </row>
     <row r="729">
-      <c r="B729" s="13"/>
+      <c r="B729" s="14"/>
     </row>
     <row r="730">
-      <c r="B730" s="13"/>
+      <c r="B730" s="14"/>
     </row>
     <row r="731">
-      <c r="B731" s="13"/>
+      <c r="B731" s="14"/>
     </row>
     <row r="732">
-      <c r="B732" s="13"/>
+      <c r="B732" s="14"/>
     </row>
     <row r="733">
-      <c r="B733" s="13"/>
+      <c r="B733" s="14"/>
     </row>
     <row r="734">
-      <c r="B734" s="13"/>
+      <c r="B734" s="14"/>
     </row>
     <row r="735">
-      <c r="B735" s="13"/>
+      <c r="B735" s="14"/>
     </row>
     <row r="736">
-      <c r="B736" s="13"/>
+      <c r="B736" s="14"/>
     </row>
     <row r="737">
-      <c r="B737" s="13"/>
+      <c r="B737" s="14"/>
     </row>
     <row r="738">
-      <c r="B738" s="13"/>
+      <c r="B738" s="14"/>
     </row>
     <row r="739">
-      <c r="B739" s="13"/>
+      <c r="B739" s="14"/>
     </row>
     <row r="740">
-      <c r="B740" s="13"/>
+      <c r="B740" s="14"/>
     </row>
     <row r="741">
-      <c r="B741" s="13"/>
+      <c r="B741" s="14"/>
     </row>
     <row r="742">
-      <c r="B742" s="13"/>
+      <c r="B742" s="14"/>
     </row>
     <row r="743">
-      <c r="B743" s="13"/>
+      <c r="B743" s="14"/>
     </row>
     <row r="744">
-      <c r="B744" s="13"/>
+      <c r="B744" s="14"/>
     </row>
     <row r="745">
-      <c r="B745" s="13"/>
+      <c r="B745" s="14"/>
     </row>
     <row r="746">
-      <c r="B746" s="13"/>
+      <c r="B746" s="14"/>
     </row>
     <row r="747">
-      <c r="B747" s="13"/>
+      <c r="B747" s="14"/>
     </row>
     <row r="748">
-      <c r="B748" s="13"/>
+      <c r="B748" s="14"/>
     </row>
     <row r="749">
-      <c r="B749" s="13"/>
+      <c r="B749" s="14"/>
     </row>
     <row r="750">
-      <c r="B750" s="13"/>
+      <c r="B750" s="14"/>
     </row>
     <row r="751">
-      <c r="B751" s="13"/>
+      <c r="B751" s="14"/>
     </row>
     <row r="752">
-      <c r="B752" s="13"/>
+      <c r="B752" s="14"/>
     </row>
     <row r="753">
-      <c r="B753" s="13"/>
+      <c r="B753" s="14"/>
     </row>
     <row r="754">
-      <c r="B754" s="13"/>
+      <c r="B754" s="14"/>
     </row>
     <row r="755">
-      <c r="B755" s="13"/>
+      <c r="B755" s="14"/>
     </row>
     <row r="756">
-      <c r="B756" s="13"/>
+      <c r="B756" s="14"/>
     </row>
     <row r="757">
-      <c r="B757" s="13"/>
+      <c r="B757" s="14"/>
     </row>
     <row r="758">
-      <c r="B758" s="13"/>
+      <c r="B758" s="14"/>
     </row>
     <row r="759">
-      <c r="B759" s="13"/>
+      <c r="B759" s="14"/>
     </row>
     <row r="760">
-      <c r="B760" s="13"/>
+      <c r="B760" s="14"/>
     </row>
     <row r="761">
-      <c r="B761" s="13"/>
+      <c r="B761" s="14"/>
     </row>
     <row r="762">
-      <c r="B762" s="13"/>
+      <c r="B762" s="14"/>
     </row>
     <row r="763">
-      <c r="B763" s="13"/>
+      <c r="B763" s="14"/>
     </row>
     <row r="764">
-      <c r="B764" s="13"/>
+      <c r="B764" s="14"/>
     </row>
     <row r="765">
-      <c r="B765" s="13"/>
+      <c r="B765" s="14"/>
     </row>
     <row r="766">
-      <c r="B766" s="13"/>
+      <c r="B766" s="14"/>
     </row>
     <row r="767">
-      <c r="B767" s="13"/>
+      <c r="B767" s="14"/>
     </row>
     <row r="768">
-      <c r="B768" s="13"/>
+      <c r="B768" s="14"/>
     </row>
     <row r="769">
-      <c r="B769" s="13"/>
+      <c r="B769" s="14"/>
     </row>
     <row r="770">
-      <c r="B770" s="13"/>
+      <c r="B770" s="14"/>
     </row>
     <row r="771">
-      <c r="B771" s="13"/>
+      <c r="B771" s="14"/>
     </row>
     <row r="772">
-      <c r="B772" s="13"/>
+      <c r="B772" s="14"/>
     </row>
     <row r="773">
-      <c r="B773" s="13"/>
+      <c r="B773" s="14"/>
     </row>
     <row r="774">
-      <c r="B774" s="13"/>
+      <c r="B774" s="14"/>
     </row>
     <row r="775">
-      <c r="B775" s="13"/>
+      <c r="B775" s="14"/>
     </row>
     <row r="776">
-      <c r="B776" s="13"/>
+      <c r="B776" s="14"/>
     </row>
     <row r="777">
-      <c r="B777" s="13"/>
+      <c r="B777" s="14"/>
     </row>
     <row r="778">
-      <c r="B778" s="13"/>
+      <c r="B778" s="14"/>
     </row>
     <row r="779">
-      <c r="B779" s="13"/>
+      <c r="B779" s="14"/>
     </row>
     <row r="780">
-      <c r="B780" s="13"/>
+      <c r="B780" s="14"/>
     </row>
     <row r="781">
-      <c r="B781" s="13"/>
+      <c r="B781" s="14"/>
     </row>
     <row r="782">
-      <c r="B782" s="13"/>
+      <c r="B782" s="14"/>
     </row>
     <row r="783">
-      <c r="B783" s="13"/>
+      <c r="B783" s="14"/>
     </row>
     <row r="784">
-      <c r="B784" s="13"/>
+      <c r="B784" s="14"/>
     </row>
     <row r="785">
-      <c r="B785" s="13"/>
+      <c r="B785" s="14"/>
     </row>
     <row r="786">
-      <c r="B786" s="13"/>
+      <c r="B786" s="14"/>
     </row>
     <row r="787">
-      <c r="B787" s="13"/>
+      <c r="B787" s="14"/>
     </row>
     <row r="788">
-      <c r="B788" s="13"/>
+      <c r="B788" s="14"/>
     </row>
     <row r="789">
-      <c r="B789" s="13"/>
+      <c r="B789" s="14"/>
     </row>
     <row r="790">
-      <c r="B790" s="13"/>
+      <c r="B790" s="14"/>
     </row>
     <row r="791">
-      <c r="B791" s="13"/>
+      <c r="B791" s="14"/>
     </row>
     <row r="792">
-      <c r="B792" s="13"/>
+      <c r="B792" s="14"/>
     </row>
     <row r="793">
-      <c r="B793" s="13"/>
+      <c r="B793" s="14"/>
     </row>
     <row r="794">
-      <c r="B794" s="13"/>
+      <c r="B794" s="14"/>
     </row>
     <row r="795">
-      <c r="B795" s="13"/>
+      <c r="B795" s="14"/>
     </row>
     <row r="796">
-      <c r="B796" s="13"/>
+      <c r="B796" s="14"/>
     </row>
     <row r="797">
-      <c r="B797" s="13"/>
+      <c r="B797" s="14"/>
     </row>
     <row r="798">
-      <c r="B798" s="13"/>
+      <c r="B798" s="14"/>
     </row>
     <row r="799">
-      <c r="B799" s="13"/>
+      <c r="B799" s="14"/>
     </row>
     <row r="800">
-      <c r="B800" s="13"/>
+      <c r="B800" s="14"/>
     </row>
     <row r="801">
-      <c r="B801" s="13"/>
+      <c r="B801" s="14"/>
     </row>
     <row r="802">
-      <c r="B802" s="13"/>
+      <c r="B802" s="14"/>
     </row>
     <row r="803">
-      <c r="B803" s="13"/>
+      <c r="B803" s="14"/>
     </row>
     <row r="804">
-      <c r="B804" s="13"/>
+      <c r="B804" s="14"/>
     </row>
     <row r="805">
-      <c r="B805" s="13"/>
+      <c r="B805" s="14"/>
     </row>
     <row r="806">
-      <c r="B806" s="13"/>
+      <c r="B806" s="14"/>
     </row>
     <row r="807">
-      <c r="B807" s="13"/>
+      <c r="B807" s="14"/>
     </row>
     <row r="808">
-      <c r="B808" s="13"/>
+      <c r="B808" s="14"/>
     </row>
     <row r="809">
-      <c r="B809" s="13"/>
+      <c r="B809" s="14"/>
     </row>
     <row r="810">
-      <c r="B810" s="13"/>
+      <c r="B810" s="14"/>
     </row>
     <row r="811">
-      <c r="B811" s="13"/>
+      <c r="B811" s="14"/>
     </row>
     <row r="812">
-      <c r="B812" s="13"/>
+      <c r="B812" s="14"/>
     </row>
     <row r="813">
-      <c r="B813" s="13"/>
+      <c r="B813" s="14"/>
     </row>
     <row r="814">
-      <c r="B814" s="13"/>
+      <c r="B814" s="14"/>
     </row>
     <row r="815">
-      <c r="B815" s="13"/>
+      <c r="B815" s="14"/>
     </row>
     <row r="816">
-      <c r="B816" s="13"/>
+      <c r="B816" s="14"/>
     </row>
     <row r="817">
-      <c r="B817" s="13"/>
+      <c r="B817" s="14"/>
     </row>
     <row r="818">
-      <c r="B818" s="13"/>
+      <c r="B818" s="14"/>
     </row>
     <row r="819">
-      <c r="B819" s="13"/>
+      <c r="B819" s="14"/>
     </row>
     <row r="820">
-      <c r="B820" s="13"/>
+      <c r="B820" s="14"/>
     </row>
     <row r="821">
-      <c r="B821" s="13"/>
+      <c r="B821" s="14"/>
     </row>
     <row r="822">
-      <c r="B822" s="13"/>
+      <c r="B822" s="14"/>
     </row>
     <row r="823">
-      <c r="B823" s="13"/>
+      <c r="B823" s="14"/>
     </row>
     <row r="824">
-      <c r="B824" s="13"/>
+      <c r="B824" s="14"/>
     </row>
     <row r="825">
-      <c r="B825" s="13"/>
+      <c r="B825" s="14"/>
     </row>
     <row r="826">
-      <c r="B826" s="13"/>
+      <c r="B826" s="14"/>
     </row>
     <row r="827">
-      <c r="B827" s="13"/>
+      <c r="B827" s="14"/>
     </row>
     <row r="828">
-      <c r="B828" s="13"/>
+      <c r="B828" s="14"/>
     </row>
     <row r="829">
-      <c r="B829" s="13"/>
+      <c r="B829" s="14"/>
     </row>
     <row r="830">
-      <c r="B830" s="13"/>
+      <c r="B830" s="14"/>
     </row>
     <row r="831">
-      <c r="B831" s="13"/>
+      <c r="B831" s="14"/>
     </row>
     <row r="832">
-      <c r="B832" s="13"/>
+      <c r="B832" s="14"/>
     </row>
     <row r="833">
-      <c r="B833" s="13"/>
+      <c r="B833" s="14"/>
     </row>
     <row r="834">
-      <c r="B834" s="13"/>
+      <c r="B834" s="14"/>
     </row>
     <row r="835">
-      <c r="B835" s="13"/>
+      <c r="B835" s="14"/>
     </row>
     <row r="836">
-      <c r="B836" s="13"/>
+      <c r="B836" s="14"/>
     </row>
     <row r="837">
-      <c r="B837" s="13"/>
+      <c r="B837" s="14"/>
     </row>
     <row r="838">
-      <c r="B838" s="13"/>
+      <c r="B838" s="14"/>
     </row>
     <row r="839">
-      <c r="B839" s="13"/>
+      <c r="B839" s="14"/>
     </row>
     <row r="840">
-      <c r="B840" s="13"/>
+      <c r="B840" s="14"/>
     </row>
     <row r="841">
-      <c r="B841" s="13"/>
+      <c r="B841" s="14"/>
     </row>
     <row r="842">
-      <c r="B842" s="13"/>
+      <c r="B842" s="14"/>
     </row>
     <row r="843">
-      <c r="B843" s="13"/>
+      <c r="B843" s="14"/>
     </row>
     <row r="844">
-      <c r="B844" s="13"/>
+      <c r="B844" s="14"/>
     </row>
     <row r="845">
-      <c r="B845" s="13"/>
+      <c r="B845" s="14"/>
     </row>
     <row r="846">
-      <c r="B846" s="13"/>
+      <c r="B846" s="14"/>
     </row>
     <row r="847">
-      <c r="B847" s="13"/>
+      <c r="B847" s="14"/>
     </row>
     <row r="848">
-      <c r="B848" s="13"/>
+      <c r="B848" s="14"/>
     </row>
     <row r="849">
-      <c r="B849" s="13"/>
+      <c r="B849" s="14"/>
     </row>
     <row r="850">
-      <c r="B850" s="13"/>
+      <c r="B850" s="14"/>
     </row>
     <row r="851">
-      <c r="B851" s="13"/>
+      <c r="B851" s="14"/>
     </row>
     <row r="852">
-      <c r="B852" s="13"/>
+      <c r="B852" s="14"/>
     </row>
     <row r="853">
-      <c r="B853" s="13"/>
+      <c r="B853" s="14"/>
     </row>
     <row r="854">
-      <c r="B854" s="13"/>
+      <c r="B854" s="14"/>
     </row>
     <row r="855">
-      <c r="B855" s="13"/>
+      <c r="B855" s="14"/>
     </row>
     <row r="856">
-      <c r="B856" s="13"/>
+      <c r="B856" s="14"/>
     </row>
     <row r="857">
-      <c r="B857" s="13"/>
+      <c r="B857" s="14"/>
     </row>
     <row r="858">
-      <c r="B858" s="13"/>
+      <c r="B858" s="14"/>
     </row>
     <row r="859">
-      <c r="B859" s="13"/>
+      <c r="B859" s="14"/>
     </row>
     <row r="860">
-      <c r="B860" s="13"/>
+      <c r="B860" s="14"/>
     </row>
     <row r="861">
-      <c r="B861" s="13"/>
+      <c r="B861" s="14"/>
     </row>
     <row r="862">
-      <c r="B862" s="13"/>
+      <c r="B862" s="14"/>
     </row>
     <row r="863">
-      <c r="B863" s="13"/>
+      <c r="B863" s="14"/>
     </row>
     <row r="864">
-      <c r="B864" s="13"/>
+      <c r="B864" s="14"/>
     </row>
     <row r="865">
-      <c r="B865" s="13"/>
+      <c r="B865" s="14"/>
     </row>
     <row r="866">
-      <c r="B866" s="13"/>
+      <c r="B866" s="14"/>
     </row>
     <row r="867">
-      <c r="B867" s="13"/>
+      <c r="B867" s="14"/>
     </row>
     <row r="868">
-      <c r="B868" s="13"/>
+      <c r="B868" s="14"/>
     </row>
     <row r="869">
-      <c r="B869" s="13"/>
+      <c r="B869" s="14"/>
     </row>
     <row r="870">
-      <c r="B870" s="13"/>
+      <c r="B870" s="14"/>
     </row>
     <row r="871">
-      <c r="B871" s="13"/>
+      <c r="B871" s="14"/>
     </row>
     <row r="872">
-      <c r="B872" s="13"/>
+      <c r="B872" s="14"/>
     </row>
     <row r="873">
-      <c r="B873" s="13"/>
+      <c r="B873" s="14"/>
     </row>
     <row r="874">
-      <c r="B874" s="13"/>
+      <c r="B874" s="14"/>
     </row>
     <row r="875">
-      <c r="B875" s="13"/>
+      <c r="B875" s="14"/>
     </row>
     <row r="876">
-      <c r="B876" s="13"/>
+      <c r="B876" s="14"/>
     </row>
     <row r="877">
-      <c r="B877" s="13"/>
+      <c r="B877" s="14"/>
     </row>
     <row r="878">
-      <c r="B878" s="13"/>
+      <c r="B878" s="14"/>
     </row>
     <row r="879">
-      <c r="B879" s="13"/>
+      <c r="B879" s="14"/>
     </row>
     <row r="880">
-      <c r="B880" s="13"/>
+      <c r="B880" s="14"/>
     </row>
     <row r="881">
-      <c r="B881" s="13"/>
+      <c r="B881" s="14"/>
     </row>
     <row r="882">
-      <c r="B882" s="13"/>
+      <c r="B882" s="14"/>
     </row>
     <row r="883">
-      <c r="B883" s="13"/>
+      <c r="B883" s="14"/>
     </row>
     <row r="884">
-      <c r="B884" s="13"/>
+      <c r="B884" s="14"/>
     </row>
     <row r="885">
-      <c r="B885" s="13"/>
+      <c r="B885" s="14"/>
     </row>
     <row r="886">
-      <c r="B886" s="13"/>
+      <c r="B886" s="14"/>
     </row>
     <row r="887">
-      <c r="B887" s="13"/>
+      <c r="B887" s="14"/>
     </row>
     <row r="888">
-      <c r="B888" s="13"/>
+      <c r="B888" s="14"/>
     </row>
     <row r="889">
-      <c r="B889" s="13"/>
+      <c r="B889" s="14"/>
     </row>
     <row r="890">
-      <c r="B890" s="13"/>
+      <c r="B890" s="14"/>
     </row>
     <row r="891">
-      <c r="B891" s="13"/>
+      <c r="B891" s="14"/>
     </row>
     <row r="892">
-      <c r="B892" s="13"/>
+      <c r="B892" s="14"/>
     </row>
     <row r="893">
-      <c r="B893" s="13"/>
+      <c r="B893" s="14"/>
     </row>
     <row r="894">
-      <c r="B894" s="13"/>
+      <c r="B894" s="14"/>
     </row>
     <row r="895">
-      <c r="B895" s="13"/>
+      <c r="B895" s="14"/>
     </row>
     <row r="896">
-      <c r="B896" s="13"/>
+      <c r="B896" s="14"/>
     </row>
     <row r="897">
-      <c r="B897" s="13"/>
+      <c r="B897" s="14"/>
     </row>
     <row r="898">
-      <c r="B898" s="13"/>
+      <c r="B898" s="14"/>
     </row>
     <row r="899">
-      <c r="B899" s="13"/>
+      <c r="B899" s="14"/>
     </row>
     <row r="900">
-      <c r="B900" s="13"/>
+      <c r="B900" s="14"/>
     </row>
     <row r="901">
-      <c r="B901" s="13"/>
+      <c r="B901" s="14"/>
     </row>
     <row r="902">
-      <c r="B902" s="13"/>
+      <c r="B902" s="14"/>
     </row>
     <row r="903">
-      <c r="B903" s="13"/>
+      <c r="B903" s="14"/>
     </row>
     <row r="904">
-      <c r="B904" s="13"/>
+      <c r="B904" s="14"/>
     </row>
     <row r="905">
-      <c r="B905" s="13"/>
+      <c r="B905" s="14"/>
     </row>
     <row r="906">
-      <c r="B906" s="13"/>
+      <c r="B906" s="14"/>
     </row>
     <row r="907">
-      <c r="B907" s="13"/>
+      <c r="B907" s="14"/>
     </row>
     <row r="908">
-      <c r="B908" s="13"/>
+      <c r="B908" s="14"/>
     </row>
     <row r="909">
-      <c r="B909" s="13"/>
+      <c r="B909" s="14"/>
     </row>
     <row r="910">
-      <c r="B910" s="13"/>
+      <c r="B910" s="14"/>
     </row>
     <row r="911">
-      <c r="B911" s="13"/>
+      <c r="B911" s="14"/>
     </row>
     <row r="912">
-      <c r="B912" s="13"/>
+      <c r="B912" s="14"/>
     </row>
     <row r="913">
-      <c r="B913" s="13"/>
+      <c r="B913" s="14"/>
     </row>
     <row r="914">
-      <c r="B914" s="13"/>
+      <c r="B914" s="14"/>
     </row>
     <row r="915">
-      <c r="B915" s="13"/>
+      <c r="B915" s="14"/>
     </row>
     <row r="916">
-      <c r="B916" s="13"/>
+      <c r="B916" s="14"/>
     </row>
     <row r="917">
-      <c r="B917" s="13"/>
+      <c r="B917" s="14"/>
     </row>
     <row r="918">
-      <c r="B918" s="13"/>
+      <c r="B918" s="14"/>
     </row>
     <row r="919">
-      <c r="B919" s="13"/>
+      <c r="B919" s="14"/>
     </row>
     <row r="920">
-      <c r="B920" s="13"/>
+      <c r="B920" s="14"/>
     </row>
     <row r="921">
-      <c r="B921" s="13"/>
+      <c r="B921" s="14"/>
     </row>
     <row r="922">
-      <c r="B922" s="13"/>
+      <c r="B922" s="14"/>
     </row>
     <row r="923">
-      <c r="B923" s="13"/>
+      <c r="B923" s="14"/>
     </row>
     <row r="924">
-      <c r="B924" s="13"/>
+      <c r="B924" s="14"/>
     </row>
     <row r="925">
-      <c r="B925" s="13"/>
+      <c r="B925" s="14"/>
     </row>
     <row r="926">
-      <c r="B926" s="13"/>
+      <c r="B926" s="14"/>
     </row>
     <row r="927">
-      <c r="B927" s="13"/>
+      <c r="B927" s="14"/>
     </row>
     <row r="928">
-      <c r="B928" s="13"/>
+      <c r="B928" s="14"/>
     </row>
     <row r="929">
-      <c r="B929" s="13"/>
+      <c r="B929" s="14"/>
     </row>
     <row r="930">
-      <c r="B930" s="13"/>
+      <c r="B930" s="14"/>
     </row>
     <row r="931">
-      <c r="B931" s="13"/>
+      <c r="B931" s="14"/>
     </row>
     <row r="932">
-      <c r="B932" s="13"/>
+      <c r="B932" s="14"/>
     </row>
     <row r="933">
-      <c r="B933" s="13"/>
+      <c r="B933" s="14"/>
     </row>
     <row r="934">
-      <c r="B934" s="13"/>
+      <c r="B934" s="14"/>
     </row>
     <row r="935">
-      <c r="B935" s="13"/>
+      <c r="B935" s="14"/>
     </row>
     <row r="936">
-      <c r="B936" s="13"/>
+      <c r="B936" s="14"/>
     </row>
     <row r="937">
-      <c r="B937" s="13"/>
+      <c r="B937" s="14"/>
     </row>
     <row r="938">
-      <c r="B938" s="13"/>
+      <c r="B938" s="14"/>
     </row>
     <row r="939">
-      <c r="B939" s="13"/>
+      <c r="B939" s="14"/>
     </row>
     <row r="940">
-      <c r="B940" s="13"/>
+      <c r="B940" s="14"/>
     </row>
     <row r="941">
-      <c r="B941" s="13"/>
+      <c r="B941" s="14"/>
     </row>
     <row r="942">
-      <c r="B942" s="13"/>
+      <c r="B942" s="14"/>
     </row>
     <row r="943">
-      <c r="B943" s="13"/>
+      <c r="B943" s="14"/>
     </row>
     <row r="944">
-      <c r="B944" s="13"/>
+      <c r="B944" s="14"/>
     </row>
     <row r="945">
-      <c r="B945" s="13"/>
+      <c r="B945" s="14"/>
     </row>
     <row r="946">
-      <c r="B946" s="13"/>
+      <c r="B946" s="14"/>
     </row>
     <row r="947">
-      <c r="B947" s="13"/>
+      <c r="B947" s="14"/>
     </row>
     <row r="948">
-      <c r="B948" s="13"/>
+      <c r="B948" s="14"/>
     </row>
     <row r="949">
-      <c r="B949" s="13"/>
+      <c r="B949" s="14"/>
     </row>
     <row r="950">
-      <c r="B950" s="13"/>
+      <c r="B950" s="14"/>
     </row>
     <row r="951">
-      <c r="B951" s="13"/>
+      <c r="B951" s="14"/>
     </row>
     <row r="952">
-      <c r="B952" s="13"/>
+      <c r="B952" s="14"/>
     </row>
     <row r="953">
-      <c r="B953" s="13"/>
+      <c r="B953" s="14"/>
     </row>
     <row r="954">
-      <c r="B954" s="13"/>
+      <c r="B954" s="14"/>
     </row>
     <row r="955">
-      <c r="B955" s="13"/>
+      <c r="B955" s="14"/>
     </row>
     <row r="956">
-      <c r="B956" s="13"/>
+      <c r="B956" s="14"/>
     </row>
     <row r="957">
-      <c r="B957" s="13"/>
+      <c r="B957" s="14"/>
     </row>
     <row r="958">
-      <c r="B958" s="13"/>
+      <c r="B958" s="14"/>
     </row>
     <row r="959">
-      <c r="B959" s="13"/>
+      <c r="B959" s="14"/>
     </row>
     <row r="960">
-      <c r="B960" s="13"/>
+      <c r="B960" s="14"/>
     </row>
     <row r="961">
-      <c r="B961" s="13"/>
+      <c r="B961" s="14"/>
     </row>
     <row r="962">
-      <c r="B962" s="13"/>
+      <c r="B962" s="14"/>
     </row>
     <row r="963">
-      <c r="B963" s="13"/>
+      <c r="B963" s="14"/>
     </row>
     <row r="964">
-      <c r="B964" s="13"/>
+      <c r="B964" s="14"/>
     </row>
     <row r="965">
-      <c r="B965" s="13"/>
+      <c r="B965" s="14"/>
     </row>
     <row r="966">
-      <c r="B966" s="13"/>
+      <c r="B966" s="14"/>
     </row>
     <row r="967">
-      <c r="B967" s="13"/>
+      <c r="B967" s="14"/>
     </row>
     <row r="968">
-      <c r="B968" s="13"/>
+      <c r="B968" s="14"/>
     </row>
     <row r="969">
-      <c r="B969" s="13"/>
+      <c r="B969" s="14"/>
     </row>
     <row r="970">
-      <c r="B970" s="13"/>
+      <c r="B970" s="14"/>
     </row>
     <row r="971">
-      <c r="B971" s="13"/>
+      <c r="B971" s="14"/>
     </row>
     <row r="972">
-      <c r="B972" s="13"/>
+      <c r="B972" s="14"/>
     </row>
     <row r="973">
-      <c r="B973" s="13"/>
+      <c r="B973" s="14"/>
     </row>
     <row r="974">
-      <c r="B974" s="13"/>
+      <c r="B974" s="14"/>
     </row>
     <row r="975">
-      <c r="B975" s="13"/>
+      <c r="B975" s="14"/>
     </row>
     <row r="976">
-      <c r="B976" s="13"/>
+      <c r="B976" s="14"/>
     </row>
     <row r="977">
-      <c r="B977" s="13"/>
+      <c r="B977" s="14"/>
     </row>
     <row r="978">
-      <c r="B978" s="13"/>
+      <c r="B978" s="14"/>
     </row>
     <row r="979">
-      <c r="B979" s="13"/>
+      <c r="B979" s="14"/>
     </row>
     <row r="980">
-      <c r="B980" s="13"/>
+      <c r="B980" s="14"/>
     </row>
     <row r="981">
-      <c r="B981" s="13"/>
+      <c r="B981" s="14"/>
     </row>
     <row r="982">
-      <c r="B982" s="13"/>
+      <c r="B982" s="14"/>
     </row>
     <row r="983">
-      <c r="B983" s="13"/>
+      <c r="B983" s="14"/>
     </row>
     <row r="984">
-      <c r="B984" s="13"/>
+      <c r="B984" s="14"/>
     </row>
     <row r="985">
-      <c r="B985" s="13"/>
+      <c r="B985" s="14"/>
     </row>
     <row r="986">
-      <c r="B986" s="13"/>
+      <c r="B986" s="14"/>
     </row>
     <row r="987">
-      <c r="B987" s="13"/>
+      <c r="B987" s="14"/>
     </row>
     <row r="988">
-      <c r="B988" s="13"/>
+      <c r="B988" s="14"/>
     </row>
     <row r="989">
-      <c r="B989" s="13"/>
+      <c r="B989" s="14"/>
     </row>
     <row r="990">
-      <c r="B990" s="13"/>
+      <c r="B990" s="14"/>
     </row>
     <row r="991">
-      <c r="B991" s="13"/>
+      <c r="B991" s="14"/>
     </row>
     <row r="992">
-      <c r="B992" s="13"/>
+      <c r="B992" s="14"/>
     </row>
     <row r="993">
-      <c r="B993" s="13"/>
+      <c r="B993" s="14"/>
     </row>
     <row r="994">
-      <c r="B994" s="13"/>
+      <c r="B994" s="14"/>
     </row>
     <row r="995">
-      <c r="B995" s="13"/>
+      <c r="B995" s="14"/>
     </row>
     <row r="996">
-      <c r="B996" s="13"/>
+      <c r="B996" s="14"/>
     </row>
     <row r="997">
-      <c r="B997" s="13"/>
+      <c r="B997" s="14"/>
     </row>
     <row r="998">
-      <c r="B998" s="13"/>
+      <c r="B998" s="14"/>
     </row>
     <row r="999">
-      <c r="B999" s="13"/>
+      <c r="B999" s="14"/>
     </row>
     <row r="1000">
-      <c r="B1000" s="13"/>
+      <c r="B1000" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="199">
   <si>
     <t>id</t>
   </si>
@@ -566,6 +566,48 @@
   </si>
   <si>
     <t>https://goo.gl/photos/6z9abe5WkQdCqYTY8</t>
+  </si>
+  <si>
+    <t>whistler</t>
+  </si>
+  <si>
+    <t>whistler blackcomb</t>
+  </si>
+  <si>
+    <t>We paid the $60 CAD for backcountry lift access, which took us to the foot of Blackcomb Glacier. From there we toured up towards The Spearhead and skiied down to Circle Lake. We then toured up the Decker Glacier and stopped for lunch at the saddle just east of Decker Mountain. We spent some time discussing whether we should ascend Decker Mountain but soon enough the weather changed and it was snowy with minimal visibility. Because of the poor visability, we were not comfortable descending or ascending anywhere. The weather remained poor much longer than we expected; we ended up building a small snow cave and sitting up on the ridge for roughly 2 hours waiting for the weather to open up. Eventually, the weather improved slightly and we followed another small group down Decker Glacier. Unfortunately, after a few turns down the steep glacier slope, it was a white out again. We waited for ~15 minutes for the visability to improve and when it did we skiied down towards the bottom of the basin. We then toured around Circle Lake up towards the Spearhead. We then descended all the way to the Whistler Village - probably a 45 minute run. When we reached Whistler Village, we literally skiied right to the side of a concert stage, where Busta Rhymes was performing. What a long, weird day.</t>
+  </si>
+  <si>
+    <t>some sluffing</t>
+  </si>
+  <si>
+    <t>Make sure you a very familiar with the weather forecast and develop a contingency plan in the case that you are stranded in a whiteout.</t>
+  </si>
+  <si>
+    <t>8.5 hours</t>
+  </si>
+  <si>
+    <t>Decker Glacier</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/fSaohPQm53VBrLeY9</t>
+  </si>
+  <si>
+    <t>joffre lakes provincial park</t>
+  </si>
+  <si>
+    <t>cayoosh mountain trailhead</t>
+  </si>
+  <si>
+    <t>We had a tentative plan to tour up Cerise Creek towards Vantage Peak. Unfortunately, we parked at the wrong trailhead and didn't realize it until we were 20 minutes into our tour. Nonetheless, we decided to continue going, with a rough objective of Mount Chief Pascal. The approach was a classic spring bushwack. My skins were globbing and I broke one of my binding risers to boot. Eventually, we reached a knob up in the alpine zone with good views. We didn't achieve our objective - or really any objective at all - but we got some good turns in through the trees back down to the car.</t>
+  </si>
+  <si>
+    <t>Make sure you are at the correct trailhead before you head out on the trail.</t>
+  </si>
+  <si>
+    <t>Joffre Lakes vicinity</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/ggiHSuUBUcTP4jVb7</t>
   </si>
 </sst>
 </file>
@@ -697,7 +739,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="11.0"/>
-    <col customWidth="1" min="3" max="3" width="18.86"/>
+    <col customWidth="1" min="3" max="3" width="23.57"/>
     <col customWidth="1" min="4" max="4" width="24.71"/>
     <col customWidth="1" min="5" max="5" width="17.86"/>
     <col customWidth="1" min="6" max="6" width="17.71"/>
@@ -2516,10 +2558,152 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="14"/>
+      <c r="A25" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="B25" s="4">
+        <v>42840.0</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>1850.0</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>7380.0</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="S25" s="3">
+        <v>7710.0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>3000.0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X25" s="6" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="14"/>
+      <c r="A26" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="B26" s="4">
+        <v>42841.0</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1100.0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>1650.0</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>4100.0</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S26" s="3">
+        <v>6700.0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>2600.0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X26" s="6" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="14"/>
@@ -5463,7 +5647,9 @@
     <hyperlink r:id="rId16" ref="X22"/>
     <hyperlink r:id="rId17" ref="X23"/>
     <hyperlink r:id="rId18" ref="X24"/>
+    <hyperlink r:id="rId19" ref="X25"/>
+    <hyperlink r:id="rId20" ref="X26"/>
   </hyperlinks>
-  <drawing r:id="rId19"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -608,6 +608,27 @@
   </si>
   <si>
     <t>https://goo.gl/photos/ggiHSuUBUcTP4jVb7</t>
+  </si>
+  <si>
+    <t>the enchantments</t>
+  </si>
+  <si>
+    <t>bridge creek campground</t>
+  </si>
+  <si>
+    <t>We stayed overnight where the gate was closed at Bridge Creek Campground. We got an alpine start and hiked the road for ~2 miles on foot before putting on skis. We skinned on the road for another mile or so until the stuart trailhead. We eventually reached colchuck lake and then ascended towards colchuck peak. At around 7200 the weather changed and visibility was reduced to ~50 feet. We waited it out for about 45 minutes and then decided that it would not be wise to continue towards the summit because of weather and the time needed to exit the tour. We grudgingly decided to transition and then enjoyed some fun turns down to colchuck lake. From the lake we had a long 8 miles of up and down to exit.</t>
+  </si>
+  <si>
+    <t>Have a good understanding of the weather forecast and know what the weather may be at various points in the tour. If we would have left an hour earlier we may have been able to reach the summit with better weather.</t>
+  </si>
+  <si>
+    <t>13 hours</t>
+  </si>
+  <si>
+    <t>Colchuck Peak</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/qZ48RYsKNQvHBpBa7</t>
   </si>
 </sst>
 </file>
@@ -2706,7 +2727,79 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14"/>
+      <c r="A27" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="4">
+        <v>42847.0</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N27" s="3">
+        <v>600.0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>1900.0</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>2100.0</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="S27" s="3">
+        <v>7200.0</v>
+      </c>
+      <c r="T27">
+        <f>S27-Q27</f>
+        <v>5100</v>
+      </c>
+      <c r="U27" s="3">
+        <v>17.8</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="14"/>
@@ -5649,7 +5742,8 @@
     <hyperlink r:id="rId18" ref="X24"/>
     <hyperlink r:id="rId19" ref="X25"/>
     <hyperlink r:id="rId20" ref="X26"/>
+    <hyperlink r:id="rId21" ref="X27"/>
   </hyperlinks>
-  <drawing r:id="rId21"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="211">
   <si>
     <t>id</t>
   </si>
@@ -629,6 +629,21 @@
   </si>
   <si>
     <t>https://goo.gl/photos/qZ48RYsKNQvHBpBa7</t>
+  </si>
+  <si>
+    <t>no rating - spring</t>
+  </si>
+  <si>
+    <t>We toured up to the north east buttress of chair peak and skiied the slopes below to snow lake. We then toured up to the ridge east of chair peak lake and then skiied the slopes below Mount Roosevelt. Then we toured across snow lake, up to snow lake divide, then skiied back to the car.</t>
+  </si>
+  <si>
+    <t>Wear sunscreen in the spring. We got sunburns amidst snow showers.</t>
+  </si>
+  <si>
+    <t>NE chair peak - E roosevelt slopes</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/UMCDftoVnHoXLNa58</t>
   </si>
 </sst>
 </file>
@@ -906,13 +921,13 @@
         <v>7 hours</v>
       </c>
       <c r="Q2" s="3">
-        <v>2600.0</v>
+        <v>3280.0</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>34</v>
       </c>
       <c r="S2" s="3">
-        <v>3600.0</v>
+        <v>4280.0</v>
       </c>
       <c r="T2" s="3">
         <v>1000.0</v>
@@ -981,13 +996,13 @@
         <v>7 hours</v>
       </c>
       <c r="Q3" s="3">
-        <v>2600.0</v>
+        <v>3280.0</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>34</v>
       </c>
       <c r="S3" s="3">
-        <v>3600.0</v>
+        <v>4280.0</v>
       </c>
       <c r="T3" s="3">
         <v>1000.0</v>
@@ -1432,13 +1447,13 @@
         <v>5.75 hours</v>
       </c>
       <c r="Q9" s="3">
-        <v>2600.0</v>
+        <v>3280.0</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>83</v>
       </c>
       <c r="S9" s="3">
-        <v>5800.0</v>
+        <v>5500.0</v>
       </c>
       <c r="T9" s="3">
         <v>3200.0</v>
@@ -1507,7 +1522,7 @@
         <v>8 hours</v>
       </c>
       <c r="Q10" s="3">
-        <v>2600.0</v>
+        <v>3280.0</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>89</v>
@@ -1808,13 +1823,13 @@
         <v>5.5 hours</v>
       </c>
       <c r="Q14" s="3">
-        <v>2600.0</v>
+        <v>3280.0</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>122</v>
       </c>
       <c r="S14" s="3">
-        <v>5800.0</v>
+        <v>5500.0</v>
       </c>
       <c r="T14" s="3">
         <v>3200.0</v>
@@ -2108,7 +2123,7 @@
         <v>9 hours</v>
       </c>
       <c r="Q18" s="3">
-        <v>2600.0</v>
+        <v>3280.0</v>
       </c>
       <c r="R18" s="5" t="s">
         <v>107</v>
@@ -2802,7 +2817,78 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="14"/>
+      <c r="A28" s="3">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="4">
+        <v>42868.0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N28" s="3">
+        <v>900.0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>1550.0</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>3280.0</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S28" s="3">
+        <v>5500.0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>4000.0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28" s="6" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="14"/>
@@ -5743,7 +5829,8 @@
     <hyperlink r:id="rId19" ref="X25"/>
     <hyperlink r:id="rId20" ref="X26"/>
     <hyperlink r:id="rId21" ref="X27"/>
+    <hyperlink r:id="rId22" ref="X28"/>
   </hyperlinks>
-  <drawing r:id="rId22"/>
+  <drawing r:id="rId23"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="216">
   <si>
     <t>id</t>
   </si>
@@ -644,6 +644,21 @@
   </si>
   <si>
     <t>https://goo.gl/photos/UMCDftoVnHoXLNa58</t>
+  </si>
+  <si>
+    <t>heliotrope ridge trailhead</t>
+  </si>
+  <si>
+    <t>We begin skinning on the road about 1 mile shy of the heliotrope ridge trailhead. Once we got to the trailhead we took the southern route through the woods up to heliotrope ridge. From there we traversed until we reached Colfax Peak. We continued skinning until we reached reached the final approach to the false summit. We then strapped on crampons and put our skis on our backs and booted the final 500-1000 feet to the false summit. From the false summit it is a casual stroll to reach the true summit. After enjoying the views we skiied from the summit and down back to the flats. Although we brought crevasse travel/rescue gear, we did not rope up at all during the tour because of great snow coverage.</t>
+  </si>
+  <si>
+    <t>Be prepared, even though you may not use all of the heavy gear that you must carry.</t>
+  </si>
+  <si>
+    <t>Mount Baker via Colman-Deming</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/gR9YH6pxYDNcwHRt8</t>
   </si>
 </sst>
 </file>
@@ -2891,7 +2906,78 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="14"/>
+      <c r="A29" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="4">
+        <v>42875.0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N29" s="3">
+        <v>550.0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1850.0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>3000.0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="S29" s="3">
+        <v>10700.0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>7700.0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>14.54</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="X29" s="6" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="14"/>
@@ -5830,7 +5916,8 @@
     <hyperlink r:id="rId20" ref="X26"/>
     <hyperlink r:id="rId21" ref="X27"/>
     <hyperlink r:id="rId22" ref="X28"/>
+    <hyperlink r:id="rId23" ref="X29"/>
   </hyperlinks>
-  <drawing r:id="rId23"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="222">
   <si>
     <t>id</t>
   </si>
@@ -659,6 +659,24 @@
   </si>
   <si>
     <t>https://goo.gl/photos/gR9YH6pxYDNcwHRt8</t>
+  </si>
+  <si>
+    <t>timberline ski area</t>
+  </si>
+  <si>
+    <t>Wes</t>
+  </si>
+  <si>
+    <t>We got an alpine start at around 430 am and from the parking lot we could already observe a line of headlights approaching the summit. The palmer snowfield eventually became icey and steep and Alyssa was not able to continue. Wes and I continued up to Hogsback and put out skis on our back for the final bootpack to the summit. The trail was busy with dozens of climbers, with a few skiiers in the mix. The pearly gates had a different form than the previous year; this year it was less steep but rather than a shelf below, the run out continued all the way to the bottom of hogsback. The 1000 feet run out was intimidating but after realizing that the bootback was easier than last year, we charged up the pearly gates. At the summit, we observed a couple snowboarders dropping north onto the cooper spur, which looked very steep. We enjoyed the views and then walked west to the spot where we were to drop in the from the summit. Even with the warm weather, the snow off the summit was hard, although skiable. We took a couple survival ski turns before crossing back over to hogsback. Below hogsback, the ski to the bottom was pure butter.</t>
+  </si>
+  <si>
+    <t>Be ambitious but cautious.</t>
+  </si>
+  <si>
+    <t>Mount Hood via Hogsback-Pearly Gates</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/XW52GNbhqsCr8PvF9</t>
   </si>
 </sst>
 </file>
@@ -2980,7 +2998,78 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="14"/>
+      <c r="A30" s="3">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="4">
+        <v>42883.0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I30" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="N30" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>1200.0</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>5900.0</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="S30" s="3">
+        <v>11250.0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>5280.0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>7.4</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="X30" s="6" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="14"/>
@@ -5917,7 +6006,8 @@
     <hyperlink r:id="rId21" ref="X27"/>
     <hyperlink r:id="rId22" ref="X28"/>
     <hyperlink r:id="rId23" ref="X29"/>
+    <hyperlink r:id="rId24" ref="X30"/>
   </hyperlinks>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId25"/>
 </worksheet>
 </file>
--- a/ski tours/Ski Tours.xlsx
+++ b/ski tours/Ski Tours.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -677,6 +677,21 @@
   </si>
   <si>
     <t>https://goo.gl/photos/XW52GNbhqsCr8PvF9</t>
+  </si>
+  <si>
+    <t>hyak forest road</t>
+  </si>
+  <si>
+    <t>We got a casual start at 900 and enjoyed a quick skin up to Silver Peak on a mild late spring day. It was great to be able to ski at snoqualmie pass in mid june due to the great snow year.</t>
+  </si>
+  <si>
+    <t>Get turns all year</t>
+  </si>
+  <si>
+    <t>silver peak</t>
+  </si>
+  <si>
+    <t>https://goo.gl/photos/55YTMEJ8Qv1yRqVx8</t>
   </si>
 </sst>
 </file>
@@ -3072,7 +3087,79 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="14"/>
+      <c r="A31" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="4">
+        <v>42897.0</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I31" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="N31" s="3">
+        <v>900.0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>1300.0</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q31">
+        <f>S31-T31</f>
+        <v>3660</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="S31" s="3">
+        <v>5300.0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1640.0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>4.6</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="W31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="X31" s="6" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="14"/>
@@ -6007,7 +6094,8 @@
     <hyperlink r:id="rId22" ref="X28"/>
     <hyperlink r:id="rId23" ref="X29"/>
     <hyperlink r:id="rId24" ref="X30"/>
+    <hyperlink r:id="rId25" ref="X31"/>
   </hyperlinks>
-  <drawing r:id="rId25"/>
+  <drawing r:id="rId26"/>
 </worksheet>
 </file>